--- a/Videos that I watched.xlsx
+++ b/Videos that I watched.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a960143ed076ae3/Desktop/Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="893" documentId="13_ncr:1_{7A07CC95-52CD-48B0-A787-62FFE8F667E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{830A16EF-F9A8-41B4-ACA1-FEB5E7A66244}"/>
+  <xr:revisionPtr revIDLastSave="995" documentId="13_ncr:1_{7A07CC95-52CD-48B0-A787-62FFE8F667E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A85949E0-7830-46E8-A5D4-865A68043215}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="2205" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2688" uniqueCount="1890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="1931">
   <si>
     <t>Date</t>
   </si>
@@ -6257,6 +6257,138 @@
   </si>
   <si>
     <t xml:space="preserve"> Ucapan PM Anwar Ibrahim ketika lancar Pusat Kecemerlangan Kajian dan Inovasi Ekonomi Islam (i-RISE) </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-NjVESCWO8w</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Yang Berhenti Menteri – EP 1 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=9jZA80SXnJ0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> What do Malaysians think about freedom of speech? - World Questions podcast, BBC World Service </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=8OuauEnIIes</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [LANGSUNG] Majlis Peluncuran Pelan Tempatan Kuala Lumpur 2040 (PTKL 2040) | 24 Jun 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=y6e6F3w4U60</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Podcast Yang Berhenti Menteri – EP 2 </t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/r/1FwEhZgRJd/</t>
+  </si>
+  <si>
+    <t>Yesterday, I was at the Singapore Rail Test Centre together with my friend, Acting Minister for Transport Jeffrey Siow, and the Johor Chief Minister, YAB Dato’ Onn Hafiz, to see for ourselves the new train that will be used for the RTS.
+This train has been completed and is currently undergoing testing. All infrastructure works for the RTS Link are also in their final phase. In a few months, this train will be moved to the Wadi Hana Depot in Johor Bahru for testing on the actual tracks.
+This shows that our project timeline is on track, and we expect the RTS Link to commence operations on 1 January 2027. The RTS Link is more than just an infrastructure project — it’s a symbol of the close relationship between Malaysia and Singapore. It will ease the daily commute of thousands of Malaysians working across the border, and serve as an economic catalyst for Johor.
+—————
+Semalam, saya berada di Singapore Rail Test Centre, bersama sahabat saya Pemangku Menteri Pengangkutan Singapura, Jeffrey Siow, dan juga Menteri Besar Johor, YAB Dato’ Onn Hafiz, untuk melihat sendiri tren baharu yang akan digunakan bagi RTS.
+Tren ini telah pun siap dan kini sedang menjalani ujian. Semua kerja pembinaan RTS Link juga berada di fasa terakhir ketika ini. Dalam beberapa bulan lagi, tren ini akan dibawa ke Depoh Wadi Hana di Johor Bahru untuk ujian di atas landasan sebenar.
+Ini menandakan jadual kerja kita berjalan lancar, dan kita menjangkakan operasi RTS Link akan bermula pada 1 Januari 2027. RTS Link bukan sekadar projek infrastruktur, tetapi simbol eratnya hubungan Malaysia dan Singapura, projek ini dijangka memudahkan perjalanan ribuan rakyat Malaysia yang berulang-alik setiap hari, dan menjadi pemangkin pembangunan ekonomi Johor.</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/r/16UR6tN3NW/</t>
+  </si>
+  <si>
+    <t>Aerotrain KLIA is finally back!</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3jmWCHKV3B4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (LIVE) Rafizi Ramli Bersama Faizal Rahman : Podcast YBM (𝗬ang 𝗕erhenti Menteri) - Episod 3 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=dHdVU7ouubY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Kaunter Bergerak Pandan </t>
+  </si>
+  <si>
+    <t>(https://www.youtube.com/live/3jmWCHKV3B4?feature=shared&amp;t=6586)
+Anwar jerit kat Rafizi for 20 minutes
+(https://www.youtube.com/live/dHdVU7ouubY?feature=shared&amp;t=7836)
+this guy leukemia</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=7-Y0nr7RPm8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (Terkini) Anthony Loke: Ucapan Penuh Di Kongres Ke-18 DAP 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=rV9Puxh5lyc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (LIVE) Rafizi Ramli Bersama Ahli-Ahli Parlimen Keadilan: Sidang Media Khas Di Puchong </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DL_95IXyF7_/</t>
+  </si>
+  <si>
+    <t>Cycled from KL to PJ</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=b1xKGVuXXKI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ASEAN meeting in Malaysia, global crises discussed </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VR4qReRZSR8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Yang Berhenti Menteri #4 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=RigILL_jrik</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Forum Awam: Integriti Kehakiman </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LPi1WpuStHE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'I'm not a lackey allowing Israel to continue in Gaza with impunity,' Malaysian PM says </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gt4RQXXl7lw</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LIVE: Himpunan Kebebasan Kehakiman! Badan Peguam berarak dari Istana Kehakiman ke pejabat PM </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=4zwV8G-BrpE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EP6 Kes Mahkamah, MUDA, Masa Depan - Syed Saddiq Jawab Semua! | Explain Sikit </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zi8muqRlQ00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EP19 | Penganggur Kabinet: Nak bersara atau ada projek lain ni? </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3iYNYXFmKxM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [[PREMIER]]13.7.25 BERANI SEMUKA - ISWARDY TANYA RAFIZI - SOALAN PANAS. DITENGKING? </t>
+  </si>
+  <si>
+    <t>actually duit dalam asb tu duit syed saddiq sebab dia finance his own campaign during 2018 election</t>
+  </si>
+  <si>
+    <t>anwar actually any ministrial position to rafizi before meeting 20 minute tengking tu. Padu dah ada and dah pakai for example the single use window app for all gov services made by digital minister. Rafizi want cash transfer monthly and apungkan minyak tapi kementerian kewangan tak nak and go for dapat subsidi kat counter. Also dalam jemaah menteri, ada menteri kata kalau apungkan minyak, election diorng kalah. rafizi praise kdn saifuddin shame. puji steven sim and nik nazmi also. fadhlina sidek tak impressive. bro rafizi said maszlee said something politically incorrect about schrizophenia based.</t>
   </si>
 </sst>
 </file>
@@ -6634,7 +6766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:E981"/>
+  <dimension ref="B3:E984"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" style="5" customWidth="1"/>
@@ -18542,10 +18674,10 @@
         <v>45732</v>
       </c>
       <c r="C853" s="3" t="s">
-        <v>1789</v>
+        <v>1907</v>
       </c>
       <c r="D853" s="7" t="s">
-        <v>1790</v>
+        <v>1908</v>
       </c>
       <c r="E853" s="3" t="s">
         <v>5</v>
@@ -18553,13 +18685,13 @@
     </row>
     <row r="854" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B854" s="5">
-        <v>45733</v>
+        <v>45732</v>
       </c>
       <c r="C854" s="3" t="s">
-        <v>1785</v>
+        <v>1789</v>
       </c>
       <c r="D854" s="7" t="s">
-        <v>1786</v>
+        <v>1790</v>
       </c>
       <c r="E854" s="3" t="s">
         <v>5</v>
@@ -18570,10 +18702,10 @@
         <v>45733</v>
       </c>
       <c r="C855" s="3" t="s">
-        <v>1791</v>
+        <v>1785</v>
       </c>
       <c r="D855" s="7" t="s">
-        <v>1792</v>
+        <v>1786</v>
       </c>
       <c r="E855" s="3" t="s">
         <v>5</v>
@@ -18581,13 +18713,13 @@
     </row>
     <row r="856" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B856" s="5">
-        <v>45737</v>
+        <v>45733</v>
       </c>
       <c r="C856" s="3" t="s">
-        <v>1797</v>
+        <v>1791</v>
       </c>
       <c r="D856" s="7" t="s">
-        <v>1798</v>
+        <v>1792</v>
       </c>
       <c r="E856" s="3" t="s">
         <v>5</v>
@@ -18598,10 +18730,10 @@
         <v>45737</v>
       </c>
       <c r="C857" s="3" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="D857" s="7" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="E857" s="3" t="s">
         <v>5</v>
@@ -18612,10 +18744,10 @@
         <v>45737</v>
       </c>
       <c r="C858" s="3" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="D858" s="7" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="E858" s="3" t="s">
         <v>5</v>
@@ -18623,13 +18755,13 @@
     </row>
     <row r="859" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B859" s="5">
-        <v>45741</v>
+        <v>45737</v>
       </c>
       <c r="C859" s="3" t="s">
-        <v>1805</v>
+        <v>1801</v>
       </c>
       <c r="D859" s="7" t="s">
-        <v>1806</v>
+        <v>1802</v>
       </c>
       <c r="E859" s="3" t="s">
         <v>5</v>
@@ -18640,7 +18772,7 @@
         <v>45741</v>
       </c>
       <c r="C860" s="3" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="D860" s="7" t="s">
         <v>1806</v>
@@ -18651,13 +18783,13 @@
     </row>
     <row r="861" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B861" s="5">
-        <v>45743</v>
+        <v>45741</v>
       </c>
       <c r="C861" s="3" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="D861" s="7" t="s">
-        <v>1809</v>
+        <v>1806</v>
       </c>
       <c r="E861" s="3" t="s">
         <v>5</v>
@@ -18665,13 +18797,13 @@
     </row>
     <row r="862" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B862" s="5">
-        <v>45748</v>
+        <v>45743</v>
       </c>
       <c r="C862" s="3" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
       <c r="D862" s="7" t="s">
-        <v>1815</v>
+        <v>1809</v>
       </c>
       <c r="E862" s="3" t="s">
         <v>5</v>
@@ -18679,13 +18811,13 @@
     </row>
     <row r="863" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B863" s="5">
-        <v>45756</v>
+        <v>45748</v>
       </c>
       <c r="C863" s="3" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="D863" s="7" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="E863" s="3" t="s">
         <v>5</v>
@@ -18693,13 +18825,13 @@
     </row>
     <row r="864" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B864" s="5">
-        <v>45758</v>
+        <v>45756</v>
       </c>
       <c r="C864" s="3" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="D864" s="7" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="E864" s="3" t="s">
         <v>5</v>
@@ -18707,13 +18839,13 @@
     </row>
     <row r="865" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B865" s="5">
-        <v>45761</v>
+        <v>45758</v>
       </c>
       <c r="C865" s="3" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="D865" s="7" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="E865" s="3" t="s">
         <v>5</v>
@@ -18721,13 +18853,13 @@
     </row>
     <row r="866" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B866" s="5">
-        <v>45766</v>
+        <v>45761</v>
       </c>
       <c r="C866" s="3" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="D866" s="7" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="E866" s="3" t="s">
         <v>5</v>
@@ -18735,27 +18867,27 @@
     </row>
     <row r="867" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B867" s="5">
+        <v>45766</v>
+      </c>
+      <c r="C867" s="3" t="s">
+        <v>1822</v>
+      </c>
+      <c r="D867" s="7" t="s">
+        <v>1823</v>
+      </c>
+      <c r="E867" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="868" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B868" s="5">
         <v>45773</v>
       </c>
-      <c r="C867" s="3" t="s">
+      <c r="C868" s="3" t="s">
         <v>1824</v>
       </c>
-      <c r="D867" s="7" t="s">
+      <c r="D868" s="7" t="s">
         <v>1825</v>
-      </c>
-      <c r="E867" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="868" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B868" s="10">
-        <v>45779</v>
-      </c>
-      <c r="C868" t="s">
-        <v>1828</v>
-      </c>
-      <c r="D868" s="7" t="s">
-        <v>1829</v>
       </c>
       <c r="E868" s="3" t="s">
         <v>5</v>
@@ -18763,13 +18895,13 @@
     </row>
     <row r="869" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B869" s="10">
-        <v>45780</v>
+        <v>45779</v>
       </c>
       <c r="C869" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="D869" s="7" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="E869" s="3" t="s">
         <v>5</v>
@@ -18777,13 +18909,13 @@
     </row>
     <row r="870" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B870" s="10">
-        <v>45783</v>
-      </c>
-      <c r="C870" s="3" t="s">
-        <v>1830</v>
+        <v>45780</v>
+      </c>
+      <c r="C870" t="s">
+        <v>1826</v>
       </c>
       <c r="D870" s="7" t="s">
-        <v>1831</v>
+        <v>1827</v>
       </c>
       <c r="E870" s="3" t="s">
         <v>5</v>
@@ -18794,10 +18926,10 @@
         <v>45783</v>
       </c>
       <c r="C871" s="3" t="s">
-        <v>1836</v>
+        <v>1830</v>
       </c>
       <c r="D871" s="7" t="s">
-        <v>1837</v>
+        <v>1831</v>
       </c>
       <c r="E871" s="3" t="s">
         <v>5</v>
@@ -18805,13 +18937,13 @@
     </row>
     <row r="872" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B872" s="10">
-        <v>45784</v>
+        <v>45783</v>
       </c>
       <c r="C872" s="3" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
       <c r="D872" s="7" t="s">
-        <v>1833</v>
+        <v>1837</v>
       </c>
       <c r="E872" s="3" t="s">
         <v>5</v>
@@ -18819,13 +18951,13 @@
     </row>
     <row r="873" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B873" s="10">
-        <v>45787</v>
+        <v>45784</v>
       </c>
       <c r="C873" s="3" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="D873" s="7" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="E873" s="3" t="s">
         <v>5</v>
@@ -18833,13 +18965,13 @@
     </row>
     <row r="874" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B874" s="10">
-        <v>45788</v>
+        <v>45787</v>
       </c>
       <c r="C874" s="3" t="s">
-        <v>1838</v>
+        <v>1834</v>
       </c>
       <c r="D874" s="7" t="s">
-        <v>1839</v>
+        <v>1835</v>
       </c>
       <c r="E874" s="3" t="s">
         <v>5</v>
@@ -18847,13 +18979,13 @@
     </row>
     <row r="875" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B875" s="10">
-        <v>45789</v>
+        <v>45788</v>
       </c>
       <c r="C875" s="3" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="D875" s="7" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="E875" s="3" t="s">
         <v>5</v>
@@ -18861,13 +18993,13 @@
     </row>
     <row r="876" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B876" s="10">
-        <v>45791</v>
+        <v>45789</v>
       </c>
       <c r="C876" s="3" t="s">
-        <v>1844</v>
+        <v>1840</v>
       </c>
       <c r="D876" s="7" t="s">
-        <v>1845</v>
+        <v>1841</v>
       </c>
       <c r="E876" s="3" t="s">
         <v>5</v>
@@ -18878,10 +19010,10 @@
         <v>45791</v>
       </c>
       <c r="C877" s="3" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="D877" s="7" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="E877" s="3" t="s">
         <v>5</v>
@@ -18889,13 +19021,13 @@
     </row>
     <row r="878" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B878" s="10">
-        <v>45792</v>
+        <v>45791</v>
       </c>
       <c r="C878" s="3" t="s">
-        <v>1846</v>
+        <v>1842</v>
       </c>
       <c r="D878" s="7" t="s">
-        <v>1847</v>
+        <v>1843</v>
       </c>
       <c r="E878" s="3" t="s">
         <v>5</v>
@@ -18903,13 +19035,13 @@
     </row>
     <row r="879" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B879" s="10">
-        <v>45793</v>
+        <v>45792</v>
       </c>
       <c r="C879" s="3" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="D879" s="7" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="E879" s="3" t="s">
         <v>5</v>
@@ -18920,10 +19052,10 @@
         <v>45793</v>
       </c>
       <c r="C880" s="3" t="s">
-        <v>1856</v>
+        <v>1848</v>
       </c>
       <c r="D880" s="7" t="s">
-        <v>1857</v>
+        <v>1849</v>
       </c>
       <c r="E880" s="3" t="s">
         <v>5</v>
@@ -18931,13 +19063,13 @@
     </row>
     <row r="881" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B881" s="10">
-        <v>45794</v>
+        <v>45793</v>
       </c>
       <c r="C881" s="3" t="s">
-        <v>1850</v>
+        <v>1856</v>
       </c>
       <c r="D881" s="7" t="s">
-        <v>1851</v>
+        <v>1857</v>
       </c>
       <c r="E881" s="3" t="s">
         <v>5</v>
@@ -18945,13 +19077,13 @@
     </row>
     <row r="882" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B882" s="10">
-        <v>45795</v>
+        <v>45794</v>
       </c>
       <c r="C882" s="3" t="s">
-        <v>1854</v>
+        <v>1850</v>
       </c>
       <c r="D882" s="7" t="s">
-        <v>1855</v>
+        <v>1851</v>
       </c>
       <c r="E882" s="3" t="s">
         <v>5</v>
@@ -18959,13 +19091,13 @@
     </row>
     <row r="883" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B883" s="10">
-        <v>45797</v>
+        <v>45795</v>
       </c>
       <c r="C883" s="3" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="D883" s="7" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="E883" s="3" t="s">
         <v>5</v>
@@ -18973,13 +19105,13 @@
     </row>
     <row r="884" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B884" s="10">
-        <v>45799</v>
+        <v>45797</v>
       </c>
       <c r="C884" s="3" t="s">
-        <v>1858</v>
+        <v>1852</v>
       </c>
       <c r="D884" s="7" t="s">
-        <v>1859</v>
+        <v>1853</v>
       </c>
       <c r="E884" s="3" t="s">
         <v>5</v>
@@ -18990,10 +19122,10 @@
         <v>45799</v>
       </c>
       <c r="C885" s="3" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="D885" s="7" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="E885" s="3" t="s">
         <v>5</v>
@@ -19001,13 +19133,13 @@
     </row>
     <row r="886" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B886" s="10">
-        <v>45800</v>
+        <v>45799</v>
       </c>
       <c r="C886" s="3" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="D886" s="7" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="E886" s="3" t="s">
         <v>5</v>
@@ -19015,13 +19147,13 @@
     </row>
     <row r="887" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B887" s="10">
-        <v>45801</v>
+        <v>45800</v>
       </c>
       <c r="C887" s="3" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="D887" s="7" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="E887" s="3" t="s">
         <v>5</v>
@@ -19032,7 +19164,7 @@
         <v>45801</v>
       </c>
       <c r="C888" s="3" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="D888" s="7" t="s">
         <v>1865</v>
@@ -19046,10 +19178,10 @@
         <v>45801</v>
       </c>
       <c r="C889" s="3" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="D889" s="7" t="s">
-        <v>1868</v>
+        <v>1865</v>
       </c>
       <c r="E889" s="3" t="s">
         <v>5</v>
@@ -19057,13 +19189,13 @@
     </row>
     <row r="890" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B890" s="10">
-        <v>45804</v>
+        <v>45801</v>
       </c>
       <c r="C890" s="3" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
       <c r="D890" s="7" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
       <c r="E890" s="3" t="s">
         <v>5</v>
@@ -19071,13 +19203,13 @@
     </row>
     <row r="891" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B891" s="10">
-        <v>45805</v>
+        <v>45804</v>
       </c>
       <c r="C891" s="3" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="D891" s="7" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="E891" s="3" t="s">
         <v>5</v>
@@ -19085,13 +19217,13 @@
     </row>
     <row r="892" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B892" s="10">
-        <v>45806</v>
+        <v>45805</v>
       </c>
       <c r="C892" s="3" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="D892" s="7" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="E892" s="3" t="s">
         <v>5</v>
@@ -19099,27 +19231,27 @@
     </row>
     <row r="893" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B893" s="10">
+        <v>45806</v>
+      </c>
+      <c r="C893" s="3" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D893" s="7" t="s">
+        <v>1874</v>
+      </c>
+      <c r="E893" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="894" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B894" s="10">
         <v>45807</v>
       </c>
-      <c r="C893" s="3" t="s">
+      <c r="C894" s="3" t="s">
         <v>1875</v>
       </c>
-      <c r="D893" s="7" t="s">
+      <c r="D894" s="7" t="s">
         <v>1876</v>
-      </c>
-      <c r="E893" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="894" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B894" s="5">
-        <v>45810</v>
-      </c>
-      <c r="C894" s="3" t="s">
-        <v>1877</v>
-      </c>
-      <c r="D894" s="7" t="s">
-        <v>1878</v>
       </c>
       <c r="E894" s="3" t="s">
         <v>5</v>
@@ -19127,13 +19259,13 @@
     </row>
     <row r="895" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B895" s="5">
-        <v>45813</v>
+        <v>45810</v>
       </c>
       <c r="C895" s="3" t="s">
-        <v>1879</v>
-      </c>
-      <c r="D895" s="2" t="s">
-        <v>1880</v>
+        <v>1877</v>
+      </c>
+      <c r="D895" s="7" t="s">
+        <v>1878</v>
       </c>
       <c r="E895" s="3" t="s">
         <v>5</v>
@@ -19144,10 +19276,10 @@
         <v>45813</v>
       </c>
       <c r="C896" s="3" t="s">
-        <v>1884</v>
-      </c>
-      <c r="D896" s="7" t="s">
-        <v>1885</v>
+        <v>1879</v>
+      </c>
+      <c r="D896" s="2" t="s">
+        <v>1880</v>
       </c>
       <c r="E896" s="3" t="s">
         <v>5</v>
@@ -19158,10 +19290,10 @@
         <v>45813</v>
       </c>
       <c r="C897" s="3" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="D897" s="7" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="E897" s="3" t="s">
         <v>5</v>
@@ -19169,48 +19301,295 @@
     </row>
     <row r="898" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B898" s="5">
+        <v>45813</v>
+      </c>
+      <c r="C898" s="3" t="s">
+        <v>1886</v>
+      </c>
+      <c r="D898" s="7" t="s">
+        <v>1887</v>
+      </c>
+      <c r="E898" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="899" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B899" s="5">
         <v>45818</v>
       </c>
-      <c r="C898" s="3" t="s">
+      <c r="C899" s="3" t="s">
         <v>1888</v>
       </c>
-      <c r="D898" s="7" t="s">
+      <c r="D899" s="7" t="s">
         <v>1889</v>
       </c>
-      <c r="E898" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="899" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="E899" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="900" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B900" s="5">
+        <v>45828</v>
+      </c>
+      <c r="C900" s="3" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D900" s="7" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E900" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="901" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B901" s="5">
+        <v>45830</v>
+      </c>
+      <c r="C901" s="3" t="s">
+        <v>1892</v>
+      </c>
+      <c r="D901" s="7" t="s">
+        <v>1893</v>
+      </c>
+      <c r="E901" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="902" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B902" s="5">
+        <v>45832</v>
+      </c>
+      <c r="C902" s="3" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D902" s="7" t="s">
+        <v>1895</v>
+      </c>
+      <c r="E902" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="903" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B903" s="5">
+        <v>45836</v>
+      </c>
+      <c r="C903" s="3" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D903" s="7" t="s">
+        <v>1897</v>
+      </c>
+      <c r="E903" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="904" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B904" s="5">
+        <v>45839</v>
+      </c>
+      <c r="C904" s="3" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D904" s="7" t="s">
+        <v>1899</v>
+      </c>
+      <c r="E904" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="905" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B905" s="5">
+        <v>45839</v>
+      </c>
+      <c r="C905" s="3" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D905" s="7" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E905" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="906" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B906" s="5">
+        <v>45842</v>
+      </c>
+      <c r="C906" s="3" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D906" s="7" t="s">
+        <v>1903</v>
+      </c>
+      <c r="E906" s="7" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="907" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B907" s="5">
+        <v>45843</v>
+      </c>
+      <c r="C907" s="3" t="s">
+        <v>1904</v>
+      </c>
+      <c r="D907" s="7" t="s">
+        <v>1905</v>
+      </c>
+      <c r="E907" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="908" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B908" s="5">
+        <v>45844</v>
+      </c>
+      <c r="C908" s="3" t="s">
+        <v>1919</v>
+      </c>
+      <c r="D908" s="7" t="s">
+        <v>1920</v>
+      </c>
+      <c r="E908" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="909" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B909" s="5">
+        <v>45845</v>
+      </c>
+      <c r="C909" s="3" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D909" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="E909" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="910" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B910" s="5">
+        <v>45849</v>
+      </c>
+      <c r="C910" s="3" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D910" s="7" t="s">
+        <v>1916</v>
+      </c>
+      <c r="E910" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="911" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B911" s="5">
+        <v>45850</v>
+      </c>
+      <c r="C911" s="3" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D911" s="7" t="s">
+        <v>1912</v>
+      </c>
+      <c r="E911" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="912" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B912" s="5">
+        <v>45851</v>
+      </c>
+      <c r="C912" s="3" t="s">
+        <v>1913</v>
+      </c>
+      <c r="D912" s="7" t="s">
+        <v>1914</v>
+      </c>
+      <c r="E912" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="913" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B913" s="5">
+        <v>45851</v>
+      </c>
+      <c r="C913" s="3" t="s">
+        <v>1917</v>
+      </c>
+      <c r="D913" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="E913" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="914" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B914" s="5">
+        <v>45851</v>
+      </c>
+      <c r="C914" s="3" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D914" s="7" t="s">
+        <v>1928</v>
+      </c>
+      <c r="E914" s="3" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="915" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B915" s="5">
+        <v>45852</v>
+      </c>
+      <c r="C915" s="3" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D915" s="7" t="s">
+        <v>1922</v>
+      </c>
+      <c r="E915" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="916" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B916" s="5">
+        <v>45852</v>
+      </c>
+      <c r="C916" s="3" t="s">
+        <v>1925</v>
+      </c>
+      <c r="D916" s="7" t="s">
+        <v>1926</v>
+      </c>
+      <c r="E916" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="917" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B917" s="5">
+        <v>45853</v>
+      </c>
+      <c r="C917" s="3" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D917" s="7" t="s">
+        <v>1924</v>
+      </c>
+      <c r="E917" s="3" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="918" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="929" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="930" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="931" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -19264,6 +19643,9 @@
     <row r="979" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="980" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="981" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Videos that I watched.xlsx
+++ b/Videos that I watched.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a960143ed076ae3/Desktop/Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="995" documentId="13_ncr:1_{7A07CC95-52CD-48B0-A787-62FFE8F667E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A85949E0-7830-46E8-A5D4-865A68043215}"/>
+  <xr:revisionPtr revIDLastSave="1219" documentId="13_ncr:1_{7A07CC95-52CD-48B0-A787-62FFE8F667E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09FB15BB-A0C4-4890-9CB7-4368322438C3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="1931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2895" uniqueCount="2028">
   <si>
     <t>Date</t>
   </si>
@@ -6389,6 +6389,314 @@
   </si>
   <si>
     <t>anwar actually any ministrial position to rafizi before meeting 20 minute tengking tu. Padu dah ada and dah pakai for example the single use window app for all gov services made by digital minister. Rafizi want cash transfer monthly and apungkan minyak tapi kementerian kewangan tak nak and go for dapat subsidi kat counter. Also dalam jemaah menteri, ada menteri kata kalau apungkan minyak, election diorng kalah. rafizi praise kdn saifuddin shame. puji steven sim and nik nazmi also. fadhlina sidek tak impressive. bro rafizi said maszlee said something politically incorrect about schrizophenia based.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=MOOfgBAO5c8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Kedua Penggal Keempat | 21 Julai 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=K4qYBhV-6fU</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=kPZB3u7g__Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Kedua Penggal Keempat | 22 Julai 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=f2PC89It4Nk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Kedua Penggal Keempat | 23 Julai 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=YqBDtZmo-Yc</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=QiU62zTJn4A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Yang Berhenti Menteri #5 </t>
+  </si>
+  <si>
+    <t>rafizi nak all the federal projects be open to everyone but the people inside reject it. Wakil rakyat pon tak tahu project apa yng kerajaan persekutuan buat</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=EPrQ4CS7Pg0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HIMPUNAN TURUN ANUAR SOGO </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PsZ40yQJl0Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 🔥LANGSUNG🔥HIMPUNAN TURUN ANWAR 2.0 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=EbHR4tJ-fy0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [LANGSUNG] Merayakan Demokrasi: Himpunan Turun Anwar di Kuala Lumpur | 26 Julai 2025 </t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@faiqinfluencermadani/video/7531367570851548423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lama tak jadi standupper dan buat liputan di luar. Harini saya cuba terjah beberapa peserta Himpunan Turun Anwar 2025. #HimpunanTurunAnwar #FYP </t>
+  </si>
+  <si>
+    <t>https://x.com/bckupacc99/status/1949038411857481877</t>
+  </si>
+  <si>
+    <t>🤔</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/anwaribrahimofficial/videos/1271461197945146/?locale=ms_MY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [LANGSUNG] Majlis Peluncuran Bulan Kebangsaan dan Kibar Jalur Gemilang 2025 | 27 Julai 2025 </t>
+  </si>
+  <si>
+    <t>anwar was kinda racist towards bangladeshi and indians???</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@mariamosman505/live?search_type=live&amp;search_id=20250727111845963CA34E2BEDE3E17BE5&amp;search_keyword=muar&amp;enter_from_merge=search_result&amp;enter_method=live_cell&amp;search_result_id=7531569801546779412</t>
+  </si>
+  <si>
+    <t>majlis peruncuran di muar</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KlMkpyPuc9c</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [LANGSUNG] Sidang Media Perkembangan Mesyuarat Khas Thailand-Kemboja | 28 Julai 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/live/QqkW07s8_Y8?feature=shared&amp;t=3368</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Kedua Penggal Keempat | 28 Julai 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=U3Q6zK9tVfY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [LANGSUNG] Pembentangan Rancangan Malaysia Ketiga Belas (RMK13) | 31 Julai 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=rJmyh9gxWnk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Yang Berhenti Menteri #7 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-aAuAwJ0WsY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LIVE: Sidang Dewan Rakyat, Rabu 6 Ogos 2025 (sesi pagi) </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=O5_q6AVZkJU</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Kedua Penggal Keempat | 6 Ogos 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Gy283nO4OA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Kedua Penggal Keempat | 4 Ogos 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=tA08tkPsc4k</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Thousands rally in Sandakan, Tawau demanding justice for Zara </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=2xRRn5l8uJ8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Justice for Zara qairina night market Tawau Sabah Malaysia ‪@bang_hat‬ 8/8/2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=xpa4q5GR7Qw</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ibu Zara Qairina Menangis Lihat J3N4Z4H, Peguam Dedah Ini Yang Terjadi, Bapa Zulfarhan Bersuara </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=GvUI7jprOMU</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hassan Karim on Mahathir, Anwar, Azmin &amp; Rafizi – No Holds Barred | with YB Hassan Karim </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mnl-2QItGBk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Kedua Penggal Keempat | 12 Ogos 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=1m39CqwuXo0</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=BvQWJbcmvZQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MSLS XIX Closing Address by YB Dato' Seri Rafizi Ramli 2025 </t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@rafiziramli/video/7537617082481921288?lang=en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sekolah adalah tempat yang sangat penting untuk kita. Sekolah bukan sahaja memberi ilmu, ia tempat memupuk budaya dan sikap.
+Bila Menteri Pendidikan Fadhlina Sidek jadi cheerleader ajak murid-murid sekolah ucapkan Happy Birthday PMX We Love You, saya kena tegur Fadhlina.
+Jangan kita campur adukkan kehendak dan kemahuan kita dengan pendidikan kanak-kanak.
+Kalau ya pun dia sangat cintakan PMX dan mahu buktikan kesetiaan, cukup dengan ucapan dari dia sendiri, tak perlu libatkan murid-murid.
+Bila dia buat begitu, nanti di masa akan datang tak salahlah menteri-menteri pendidikan akan datang meminta murid-murid, pelajar dan siswa menyatakan taat setia dan kecintaan kepada pemimpin lain.
+Sedangkan sekolah tidak boleh dicampur adukkan dengan politik dan pandangan peribadi kita.
+Saya cukup berhati-hati dengan sekolah. Sepanjang saya jadi Ahli Parlimen, sebaik mungkin saya bantu permohonan sekolah-sekolah di Pandan. Tapi saya hanya hadir ke dalam kawasan sekolah sekali sahaja, itu pun sebab dipujuk sangat oleh guru besar.
+Sebabnya ialah saya tidak mahu campur adukkan politik dengan sekolah dan anak-anak kita.
+Saya tahu kalau orang lain buat, saya akan marah.
+Tapi kini bila Menteri Pendidikan dari PKR sendiri yang buat, saya pun rasa malu.
+Lepas ni orang PKR tak boleh kritik dah kalau ada ahli politik masuk sekolah dengan mesej politik.
+#rafiziramli #SekolahBukanPolitik #AnakKitaBukanAlat #PolitikDalamSekolah #kementerianpendidikan </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=7T1_TjZPgrc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Kedua Penggal Keempat | 13 Ogos 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=pD85GtAcafI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Sidang Media oleh YB Dato' Seri Mohd Rafizi Ramli, Ahli Parlimen Pandan | 14 Ogos 2025 </t>
+  </si>
+  <si>
+    <t>https://www.reddit.com/r/malaysia/comments/1mqrzj4/school_zone_road_makeover_to_make_it_safer_for/</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> School zone road makeover to make it safer for pedestrians. </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/19YDp_rC-nk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Prime Minister Anwar Shares a Humorous Moment with Syed Saddiq </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hDQLr8WvTjA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Yang Berhenti Menteri Episode 9 - YB Rafizi Ramli, YB Rodziah &amp; Victor Tan </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=iWi7HJe346s</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Temu Anwar @MMU </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Bx9FVjxUxu8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Kedua Penggal Keempat | 20 Ogos 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=n9EHidcsno4</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@rafiziramli/video/7540517097806302472?lang=en</t>
+  </si>
+  <si>
+    <t>BUKAN ISMAIL SABRI, BUKAN KJ
+Ada yang cuba kaitkan serangan ke atas anak saya dengan Ismail Sabri atau KJ. Saya tak selidik atau sentuh kedua-duanya, ini cubaan jahat mengalihkan perhatian.
+Rentetan dari insiden satu serangan ke atas anak saya minggu lepas, soalan yang sering berlegar ialah siapa dalang yang mengarahkan serangan itu.
+Serangan itu diikuti dengan mesej-mesej ugutan yang mahukan saya diam. Jadi timbul persoalan siapa yang mahu saya diam dan diam mengenai isu apa.
+Saya telah mengesahkan bahawa seminggu sebelum serangan, memang saya ada berjumpa dengan pemberi maklumat mengenai satu skandal yang saya sedang teliti.
+Selepas kenyataan itu, saya lihat tiba-tiba ada tuduhan-tuduhan yang berlegar.
+Tuduhan pertama, kononnya saya sedang meneliti satu kes yang melibatkan mantan Perdana Menteri, Dato’ Seri Ismail Sabri Yaakob. Konon melibatkan wang yang dicuci di luar negara.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=88lKLZdXLvg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Kedua Penggal Keempat | 21 Ogos 2025 </t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@rafiziramli/video/7540884802489076999?lang=en</t>
+  </si>
+  <si>
+    <t>This week, Tan Sri Muhyiddin Yassin announced that PN will merge with 12 other political parties outside the government to form a common platform.This</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gS5ezTLPVrQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EP 30 | 'Apa dah jadi dengan PKR?' bersama Faizal Rahman </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=UAm83bLEhDg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (LIVE) Rafizi Ramli Bersama Iqbal Fatkhi &amp; Chak Onn Lau: Podcast YBM - Episod 10 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=AJ30t63H0Vs</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Kedua Penggal Keempat | 25 Ogos 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=NDUAIFqRRns</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=4-KSALr_LA8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Kedua Penggal Keempat | 26 Ogos 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=qQM3Zg2ySls</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=X17JsKEHggI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Kedua Penggal Keempat | 27 Ogos 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=fpwD_4oqHJ0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Kedua Penggal Keempat | 28 Ogos 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=O_e3CnrTkV4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> UKM mempertahankan hak bumiputera." - Prof. Dr. Sufian Jusoh, Naib Canselor UKM. </t>
+  </si>
+  <si>
+    <t>hidayah dad is pro bumiputera</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Ho-yj5nWYlY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [PENUH] Perbarisan Dan Perarakan Sambutan Hari Kebangsaan 2025 | 31 Ogos 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gMY5R36x-mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Yang Berhenti Menteri Episod 11 | Merdeka Dahulu, Merdeka Sekarang </t>
   </si>
 </sst>
 </file>
@@ -6766,7 +7074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:E984"/>
+  <dimension ref="B3:E990"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" style="5" customWidth="1"/>
@@ -18559,13 +18867,13 @@
     </row>
     <row r="845" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B845" s="5">
-        <v>45726</v>
+        <v>45722</v>
       </c>
       <c r="C845" s="3" t="s">
-        <v>1775</v>
+        <v>1992</v>
       </c>
       <c r="D845" s="7" t="s">
-        <v>1776</v>
+        <v>1993</v>
       </c>
       <c r="E845" s="3" t="s">
         <v>5</v>
@@ -18573,13 +18881,13 @@
     </row>
     <row r="846" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B846" s="5">
-        <v>45727</v>
+        <v>45726</v>
       </c>
       <c r="C846" s="3" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="D846" s="7" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="E846" s="3" t="s">
         <v>5</v>
@@ -18587,13 +18895,13 @@
     </row>
     <row r="847" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B847" s="5">
-        <v>45729</v>
+        <v>45727</v>
       </c>
       <c r="C847" s="3" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="D847" s="7" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="E847" s="3" t="s">
         <v>5</v>
@@ -18601,13 +18909,13 @@
     </row>
     <row r="848" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B848" s="5">
-        <v>45730</v>
+        <v>45729</v>
       </c>
       <c r="C848" s="3" t="s">
-        <v>1793</v>
+        <v>1779</v>
       </c>
       <c r="D848" s="7" t="s">
-        <v>1794</v>
+        <v>1780</v>
       </c>
       <c r="E848" s="3" t="s">
         <v>5</v>
@@ -18615,13 +18923,13 @@
     </row>
     <row r="849" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B849" s="5">
-        <v>45731</v>
+        <v>45730</v>
       </c>
       <c r="C849" s="3" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D849" s="7" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="E849" s="3" t="s">
         <v>5</v>
@@ -18629,13 +18937,13 @@
     </row>
     <row r="850" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B850" s="5">
-        <v>45732</v>
+        <v>45731</v>
       </c>
       <c r="C850" s="3" t="s">
-        <v>1781</v>
-      </c>
-      <c r="D850" s="2" t="s">
-        <v>1782</v>
+        <v>1795</v>
+      </c>
+      <c r="D850" s="7" t="s">
+        <v>1796</v>
       </c>
       <c r="E850" s="3" t="s">
         <v>5</v>
@@ -18646,10 +18954,10 @@
         <v>45732</v>
       </c>
       <c r="C851" s="3" t="s">
-        <v>1783</v>
-      </c>
-      <c r="D851" s="7" t="s">
-        <v>1784</v>
+        <v>1781</v>
+      </c>
+      <c r="D851" s="2" t="s">
+        <v>1782</v>
       </c>
       <c r="E851" s="3" t="s">
         <v>5</v>
@@ -18660,10 +18968,10 @@
         <v>45732</v>
       </c>
       <c r="C852" s="3" t="s">
-        <v>1787</v>
+        <v>1783</v>
       </c>
       <c r="D852" s="7" t="s">
-        <v>1788</v>
+        <v>1784</v>
       </c>
       <c r="E852" s="3" t="s">
         <v>5</v>
@@ -18674,10 +18982,10 @@
         <v>45732</v>
       </c>
       <c r="C853" s="3" t="s">
-        <v>1907</v>
+        <v>1787</v>
       </c>
       <c r="D853" s="7" t="s">
-        <v>1908</v>
+        <v>1788</v>
       </c>
       <c r="E853" s="3" t="s">
         <v>5</v>
@@ -18688,10 +18996,10 @@
         <v>45732</v>
       </c>
       <c r="C854" s="3" t="s">
-        <v>1789</v>
+        <v>1907</v>
       </c>
       <c r="D854" s="7" t="s">
-        <v>1790</v>
+        <v>1908</v>
       </c>
       <c r="E854" s="3" t="s">
         <v>5</v>
@@ -18699,13 +19007,13 @@
     </row>
     <row r="855" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B855" s="5">
-        <v>45733</v>
+        <v>45732</v>
       </c>
       <c r="C855" s="3" t="s">
-        <v>1785</v>
+        <v>1789</v>
       </c>
       <c r="D855" s="7" t="s">
-        <v>1786</v>
+        <v>1790</v>
       </c>
       <c r="E855" s="3" t="s">
         <v>5</v>
@@ -18716,10 +19024,10 @@
         <v>45733</v>
       </c>
       <c r="C856" s="3" t="s">
-        <v>1791</v>
+        <v>1785</v>
       </c>
       <c r="D856" s="7" t="s">
-        <v>1792</v>
+        <v>1786</v>
       </c>
       <c r="E856" s="3" t="s">
         <v>5</v>
@@ -18727,13 +19035,13 @@
     </row>
     <row r="857" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B857" s="5">
-        <v>45737</v>
+        <v>45733</v>
       </c>
       <c r="C857" s="3" t="s">
-        <v>1797</v>
+        <v>1791</v>
       </c>
       <c r="D857" s="7" t="s">
-        <v>1798</v>
+        <v>1792</v>
       </c>
       <c r="E857" s="3" t="s">
         <v>5</v>
@@ -18744,10 +19052,10 @@
         <v>45737</v>
       </c>
       <c r="C858" s="3" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="D858" s="7" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="E858" s="3" t="s">
         <v>5</v>
@@ -18758,10 +19066,10 @@
         <v>45737</v>
       </c>
       <c r="C859" s="3" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="D859" s="7" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="E859" s="3" t="s">
         <v>5</v>
@@ -18769,13 +19077,13 @@
     </row>
     <row r="860" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B860" s="5">
-        <v>45741</v>
+        <v>45737</v>
       </c>
       <c r="C860" s="3" t="s">
-        <v>1805</v>
+        <v>1801</v>
       </c>
       <c r="D860" s="7" t="s">
-        <v>1806</v>
+        <v>1802</v>
       </c>
       <c r="E860" s="3" t="s">
         <v>5</v>
@@ -18786,7 +19094,7 @@
         <v>45741</v>
       </c>
       <c r="C861" s="3" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="D861" s="7" t="s">
         <v>1806</v>
@@ -18797,13 +19105,13 @@
     </row>
     <row r="862" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B862" s="5">
-        <v>45743</v>
+        <v>45741</v>
       </c>
       <c r="C862" s="3" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="D862" s="7" t="s">
-        <v>1809</v>
+        <v>1806</v>
       </c>
       <c r="E862" s="3" t="s">
         <v>5</v>
@@ -18811,13 +19119,13 @@
     </row>
     <row r="863" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B863" s="5">
-        <v>45748</v>
+        <v>45743</v>
       </c>
       <c r="C863" s="3" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
       <c r="D863" s="7" t="s">
-        <v>1815</v>
+        <v>1809</v>
       </c>
       <c r="E863" s="3" t="s">
         <v>5</v>
@@ -18825,13 +19133,13 @@
     </row>
     <row r="864" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B864" s="5">
-        <v>45756</v>
+        <v>45748</v>
       </c>
       <c r="C864" s="3" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="D864" s="7" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="E864" s="3" t="s">
         <v>5</v>
@@ -18839,13 +19147,13 @@
     </row>
     <row r="865" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B865" s="5">
-        <v>45758</v>
+        <v>45756</v>
       </c>
       <c r="C865" s="3" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="D865" s="7" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="E865" s="3" t="s">
         <v>5</v>
@@ -18853,13 +19161,13 @@
     </row>
     <row r="866" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B866" s="5">
-        <v>45761</v>
+        <v>45758</v>
       </c>
       <c r="C866" s="3" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="D866" s="7" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="E866" s="3" t="s">
         <v>5</v>
@@ -18867,13 +19175,13 @@
     </row>
     <row r="867" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B867" s="5">
-        <v>45766</v>
+        <v>45761</v>
       </c>
       <c r="C867" s="3" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="D867" s="7" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="E867" s="3" t="s">
         <v>5</v>
@@ -18881,27 +19189,27 @@
     </row>
     <row r="868" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B868" s="5">
+        <v>45766</v>
+      </c>
+      <c r="C868" s="3" t="s">
+        <v>1822</v>
+      </c>
+      <c r="D868" s="7" t="s">
+        <v>1823</v>
+      </c>
+      <c r="E868" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="869" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B869" s="5">
         <v>45773</v>
       </c>
-      <c r="C868" s="3" t="s">
+      <c r="C869" s="3" t="s">
         <v>1824</v>
       </c>
-      <c r="D868" s="7" t="s">
+      <c r="D869" s="7" t="s">
         <v>1825</v>
-      </c>
-      <c r="E868" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="869" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B869" s="10">
-        <v>45779</v>
-      </c>
-      <c r="C869" t="s">
-        <v>1828</v>
-      </c>
-      <c r="D869" s="7" t="s">
-        <v>1829</v>
       </c>
       <c r="E869" s="3" t="s">
         <v>5</v>
@@ -18909,13 +19217,13 @@
     </row>
     <row r="870" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B870" s="10">
-        <v>45780</v>
+        <v>45779</v>
       </c>
       <c r="C870" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="D870" s="7" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="E870" s="3" t="s">
         <v>5</v>
@@ -18923,13 +19231,13 @@
     </row>
     <row r="871" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B871" s="10">
-        <v>45783</v>
-      </c>
-      <c r="C871" s="3" t="s">
-        <v>1830</v>
+        <v>45780</v>
+      </c>
+      <c r="C871" t="s">
+        <v>1826</v>
       </c>
       <c r="D871" s="7" t="s">
-        <v>1831</v>
+        <v>1827</v>
       </c>
       <c r="E871" s="3" t="s">
         <v>5</v>
@@ -18940,10 +19248,10 @@
         <v>45783</v>
       </c>
       <c r="C872" s="3" t="s">
-        <v>1836</v>
+        <v>1830</v>
       </c>
       <c r="D872" s="7" t="s">
-        <v>1837</v>
+        <v>1831</v>
       </c>
       <c r="E872" s="3" t="s">
         <v>5</v>
@@ -18951,13 +19259,13 @@
     </row>
     <row r="873" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B873" s="10">
-        <v>45784</v>
+        <v>45783</v>
       </c>
       <c r="C873" s="3" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
       <c r="D873" s="7" t="s">
-        <v>1833</v>
+        <v>1837</v>
       </c>
       <c r="E873" s="3" t="s">
         <v>5</v>
@@ -18965,13 +19273,13 @@
     </row>
     <row r="874" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B874" s="10">
-        <v>45787</v>
+        <v>45784</v>
       </c>
       <c r="C874" s="3" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="D874" s="7" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="E874" s="3" t="s">
         <v>5</v>
@@ -18979,13 +19287,13 @@
     </row>
     <row r="875" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B875" s="10">
-        <v>45788</v>
+        <v>45787</v>
       </c>
       <c r="C875" s="3" t="s">
-        <v>1838</v>
+        <v>1834</v>
       </c>
       <c r="D875" s="7" t="s">
-        <v>1839</v>
+        <v>1835</v>
       </c>
       <c r="E875" s="3" t="s">
         <v>5</v>
@@ -18993,13 +19301,13 @@
     </row>
     <row r="876" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B876" s="10">
-        <v>45789</v>
+        <v>45788</v>
       </c>
       <c r="C876" s="3" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="D876" s="7" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="E876" s="3" t="s">
         <v>5</v>
@@ -19007,13 +19315,13 @@
     </row>
     <row r="877" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B877" s="10">
-        <v>45791</v>
+        <v>45789</v>
       </c>
       <c r="C877" s="3" t="s">
-        <v>1844</v>
+        <v>1840</v>
       </c>
       <c r="D877" s="7" t="s">
-        <v>1845</v>
+        <v>1841</v>
       </c>
       <c r="E877" s="3" t="s">
         <v>5</v>
@@ -19024,10 +19332,10 @@
         <v>45791</v>
       </c>
       <c r="C878" s="3" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="D878" s="7" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="E878" s="3" t="s">
         <v>5</v>
@@ -19035,13 +19343,13 @@
     </row>
     <row r="879" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B879" s="10">
-        <v>45792</v>
+        <v>45791</v>
       </c>
       <c r="C879" s="3" t="s">
-        <v>1846</v>
+        <v>1842</v>
       </c>
       <c r="D879" s="7" t="s">
-        <v>1847</v>
+        <v>1843</v>
       </c>
       <c r="E879" s="3" t="s">
         <v>5</v>
@@ -19049,13 +19357,13 @@
     </row>
     <row r="880" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B880" s="10">
-        <v>45793</v>
+        <v>45792</v>
       </c>
       <c r="C880" s="3" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="D880" s="7" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="E880" s="3" t="s">
         <v>5</v>
@@ -19066,10 +19374,10 @@
         <v>45793</v>
       </c>
       <c r="C881" s="3" t="s">
-        <v>1856</v>
+        <v>1848</v>
       </c>
       <c r="D881" s="7" t="s">
-        <v>1857</v>
+        <v>1849</v>
       </c>
       <c r="E881" s="3" t="s">
         <v>5</v>
@@ -19077,13 +19385,13 @@
     </row>
     <row r="882" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B882" s="10">
-        <v>45794</v>
+        <v>45793</v>
       </c>
       <c r="C882" s="3" t="s">
-        <v>1850</v>
+        <v>1856</v>
       </c>
       <c r="D882" s="7" t="s">
-        <v>1851</v>
+        <v>1857</v>
       </c>
       <c r="E882" s="3" t="s">
         <v>5</v>
@@ -19091,13 +19399,13 @@
     </row>
     <row r="883" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B883" s="10">
-        <v>45795</v>
+        <v>45794</v>
       </c>
       <c r="C883" s="3" t="s">
-        <v>1854</v>
+        <v>1850</v>
       </c>
       <c r="D883" s="7" t="s">
-        <v>1855</v>
+        <v>1851</v>
       </c>
       <c r="E883" s="3" t="s">
         <v>5</v>
@@ -19105,13 +19413,13 @@
     </row>
     <row r="884" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B884" s="10">
-        <v>45797</v>
+        <v>45795</v>
       </c>
       <c r="C884" s="3" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="D884" s="7" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="E884" s="3" t="s">
         <v>5</v>
@@ -19119,13 +19427,13 @@
     </row>
     <row r="885" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B885" s="10">
-        <v>45799</v>
+        <v>45797</v>
       </c>
       <c r="C885" s="3" t="s">
-        <v>1858</v>
+        <v>1852</v>
       </c>
       <c r="D885" s="7" t="s">
-        <v>1859</v>
+        <v>1853</v>
       </c>
       <c r="E885" s="3" t="s">
         <v>5</v>
@@ -19136,10 +19444,10 @@
         <v>45799</v>
       </c>
       <c r="C886" s="3" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="D886" s="7" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="E886" s="3" t="s">
         <v>5</v>
@@ -19147,13 +19455,13 @@
     </row>
     <row r="887" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B887" s="10">
-        <v>45800</v>
+        <v>45799</v>
       </c>
       <c r="C887" s="3" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="D887" s="7" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="E887" s="3" t="s">
         <v>5</v>
@@ -19161,13 +19469,13 @@
     </row>
     <row r="888" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B888" s="10">
-        <v>45801</v>
+        <v>45800</v>
       </c>
       <c r="C888" s="3" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="D888" s="7" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="E888" s="3" t="s">
         <v>5</v>
@@ -19178,7 +19486,7 @@
         <v>45801</v>
       </c>
       <c r="C889" s="3" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="D889" s="7" t="s">
         <v>1865</v>
@@ -19192,10 +19500,10 @@
         <v>45801</v>
       </c>
       <c r="C890" s="3" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="D890" s="7" t="s">
-        <v>1868</v>
+        <v>1865</v>
       </c>
       <c r="E890" s="3" t="s">
         <v>5</v>
@@ -19203,13 +19511,13 @@
     </row>
     <row r="891" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B891" s="10">
-        <v>45804</v>
+        <v>45801</v>
       </c>
       <c r="C891" s="3" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
       <c r="D891" s="7" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
       <c r="E891" s="3" t="s">
         <v>5</v>
@@ -19217,13 +19525,13 @@
     </row>
     <row r="892" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B892" s="10">
-        <v>45805</v>
+        <v>45804</v>
       </c>
       <c r="C892" s="3" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="D892" s="7" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="E892" s="3" t="s">
         <v>5</v>
@@ -19231,13 +19539,13 @@
     </row>
     <row r="893" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B893" s="10">
-        <v>45806</v>
+        <v>45805</v>
       </c>
       <c r="C893" s="3" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="D893" s="7" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="E893" s="3" t="s">
         <v>5</v>
@@ -19245,27 +19553,27 @@
     </row>
     <row r="894" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B894" s="10">
+        <v>45806</v>
+      </c>
+      <c r="C894" s="3" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D894" s="7" t="s">
+        <v>1874</v>
+      </c>
+      <c r="E894" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="895" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B895" s="10">
         <v>45807</v>
       </c>
-      <c r="C894" s="3" t="s">
+      <c r="C895" s="3" t="s">
         <v>1875</v>
       </c>
-      <c r="D894" s="7" t="s">
+      <c r="D895" s="7" t="s">
         <v>1876</v>
-      </c>
-      <c r="E894" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="895" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B895" s="5">
-        <v>45810</v>
-      </c>
-      <c r="C895" s="3" t="s">
-        <v>1877</v>
-      </c>
-      <c r="D895" s="7" t="s">
-        <v>1878</v>
       </c>
       <c r="E895" s="3" t="s">
         <v>5</v>
@@ -19273,13 +19581,13 @@
     </row>
     <row r="896" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B896" s="5">
-        <v>45813</v>
+        <v>45810</v>
       </c>
       <c r="C896" s="3" t="s">
-        <v>1879</v>
-      </c>
-      <c r="D896" s="2" t="s">
-        <v>1880</v>
+        <v>1877</v>
+      </c>
+      <c r="D896" s="7" t="s">
+        <v>1878</v>
       </c>
       <c r="E896" s="3" t="s">
         <v>5</v>
@@ -19290,10 +19598,10 @@
         <v>45813</v>
       </c>
       <c r="C897" s="3" t="s">
-        <v>1884</v>
-      </c>
-      <c r="D897" s="7" t="s">
-        <v>1885</v>
+        <v>1879</v>
+      </c>
+      <c r="D897" s="2" t="s">
+        <v>1880</v>
       </c>
       <c r="E897" s="3" t="s">
         <v>5</v>
@@ -19304,10 +19612,10 @@
         <v>45813</v>
       </c>
       <c r="C898" s="3" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="D898" s="7" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="E898" s="3" t="s">
         <v>5</v>
@@ -19315,13 +19623,13 @@
     </row>
     <row r="899" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B899" s="5">
-        <v>45818</v>
+        <v>45813</v>
       </c>
       <c r="C899" s="3" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="D899" s="7" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="E899" s="3" t="s">
         <v>5</v>
@@ -19329,13 +19637,13 @@
     </row>
     <row r="900" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B900" s="5">
-        <v>45828</v>
+        <v>45818</v>
       </c>
       <c r="C900" s="3" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="D900" s="7" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="E900" s="3" t="s">
         <v>5</v>
@@ -19343,13 +19651,13 @@
     </row>
     <row r="901" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B901" s="5">
-        <v>45830</v>
+        <v>45828</v>
       </c>
       <c r="C901" s="3" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="D901" s="7" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="E901" s="3" t="s">
         <v>5</v>
@@ -19357,13 +19665,13 @@
     </row>
     <row r="902" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B902" s="5">
-        <v>45832</v>
+        <v>45830</v>
       </c>
       <c r="C902" s="3" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="D902" s="7" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="E902" s="3" t="s">
         <v>5</v>
@@ -19371,13 +19679,13 @@
     </row>
     <row r="903" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B903" s="5">
-        <v>45836</v>
+        <v>45832</v>
       </c>
       <c r="C903" s="3" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="D903" s="7" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="E903" s="3" t="s">
         <v>5</v>
@@ -19385,13 +19693,13 @@
     </row>
     <row r="904" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B904" s="5">
-        <v>45839</v>
+        <v>45836</v>
       </c>
       <c r="C904" s="3" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="D904" s="7" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="E904" s="3" t="s">
         <v>5</v>
@@ -19402,10 +19710,10 @@
         <v>45839</v>
       </c>
       <c r="C905" s="3" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="D905" s="7" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="E905" s="3" t="s">
         <v>5</v>
@@ -19413,41 +19721,41 @@
     </row>
     <row r="906" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B906" s="5">
-        <v>45842</v>
+        <v>45839</v>
       </c>
       <c r="C906" s="3" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="D906" s="7" t="s">
-        <v>1903</v>
-      </c>
-      <c r="E906" s="7" t="s">
-        <v>1906</v>
+        <v>1901</v>
+      </c>
+      <c r="E906" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="907" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B907" s="5">
-        <v>45843</v>
+        <v>45842</v>
       </c>
       <c r="C907" s="3" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="D907" s="7" t="s">
-        <v>1905</v>
-      </c>
-      <c r="E907" s="3" t="s">
-        <v>5</v>
+        <v>1903</v>
+      </c>
+      <c r="E907" s="7" t="s">
+        <v>1906</v>
       </c>
     </row>
     <row r="908" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B908" s="5">
-        <v>45844</v>
+        <v>45843</v>
       </c>
       <c r="C908" s="3" t="s">
-        <v>1919</v>
+        <v>1904</v>
       </c>
       <c r="D908" s="7" t="s">
-        <v>1920</v>
+        <v>1905</v>
       </c>
       <c r="E908" s="3" t="s">
         <v>5</v>
@@ -19455,13 +19763,13 @@
     </row>
     <row r="909" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B909" s="5">
-        <v>45845</v>
+        <v>45844</v>
       </c>
       <c r="C909" s="3" t="s">
-        <v>1909</v>
+        <v>1919</v>
       </c>
       <c r="D909" s="7" t="s">
-        <v>1910</v>
+        <v>1920</v>
       </c>
       <c r="E909" s="3" t="s">
         <v>5</v>
@@ -19469,13 +19777,13 @@
     </row>
     <row r="910" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B910" s="5">
-        <v>45849</v>
+        <v>45845</v>
       </c>
       <c r="C910" s="3" t="s">
-        <v>1915</v>
+        <v>1909</v>
       </c>
       <c r="D910" s="7" t="s">
-        <v>1916</v>
+        <v>1910</v>
       </c>
       <c r="E910" s="3" t="s">
         <v>5</v>
@@ -19483,13 +19791,13 @@
     </row>
     <row r="911" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B911" s="5">
-        <v>45850</v>
+        <v>45849</v>
       </c>
       <c r="C911" s="3" t="s">
-        <v>1911</v>
+        <v>1915</v>
       </c>
       <c r="D911" s="7" t="s">
-        <v>1912</v>
+        <v>1916</v>
       </c>
       <c r="E911" s="3" t="s">
         <v>5</v>
@@ -19497,13 +19805,13 @@
     </row>
     <row r="912" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B912" s="5">
-        <v>45851</v>
+        <v>45850</v>
       </c>
       <c r="C912" s="3" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="D912" s="7" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="E912" s="3" t="s">
         <v>5</v>
@@ -19514,10 +19822,10 @@
         <v>45851</v>
       </c>
       <c r="C913" s="3" t="s">
-        <v>1917</v>
+        <v>1913</v>
       </c>
       <c r="D913" s="7" t="s">
-        <v>1918</v>
+        <v>1914</v>
       </c>
       <c r="E913" s="3" t="s">
         <v>5</v>
@@ -19528,27 +19836,27 @@
         <v>45851</v>
       </c>
       <c r="C914" s="3" t="s">
-        <v>1927</v>
+        <v>1917</v>
       </c>
       <c r="D914" s="7" t="s">
-        <v>1928</v>
+        <v>1918</v>
       </c>
       <c r="E914" s="3" t="s">
-        <v>1930</v>
+        <v>5</v>
       </c>
     </row>
     <row r="915" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B915" s="5">
-        <v>45852</v>
+        <v>45851</v>
       </c>
       <c r="C915" s="3" t="s">
-        <v>1921</v>
+        <v>1927</v>
       </c>
       <c r="D915" s="7" t="s">
-        <v>1922</v>
+        <v>1928</v>
       </c>
       <c r="E915" s="3" t="s">
-        <v>5</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="916" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -19556,10 +19864,10 @@
         <v>45852</v>
       </c>
       <c r="C916" s="3" t="s">
-        <v>1925</v>
+        <v>1921</v>
       </c>
       <c r="D916" s="7" t="s">
-        <v>1926</v>
+        <v>1922</v>
       </c>
       <c r="E916" s="3" t="s">
         <v>5</v>
@@ -19567,77 +19875,727 @@
     </row>
     <row r="917" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B917" s="5">
+        <v>45852</v>
+      </c>
+      <c r="C917" s="3" t="s">
+        <v>1925</v>
+      </c>
+      <c r="D917" s="7" t="s">
+        <v>1926</v>
+      </c>
+      <c r="E917" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="918" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B918" s="5">
         <v>45853</v>
       </c>
-      <c r="C917" s="3" t="s">
+      <c r="C918" s="3" t="s">
         <v>1923</v>
       </c>
-      <c r="D917" s="7" t="s">
+      <c r="D918" s="7" t="s">
         <v>1924</v>
       </c>
-      <c r="E917" s="3" t="s">
+      <c r="E918" s="3" t="s">
         <v>1929</v>
       </c>
     </row>
-    <row r="918" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B919" s="5">
+        <v>45856</v>
+      </c>
+      <c r="C919" s="3" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D919" s="7" t="s">
+        <v>1940</v>
+      </c>
+      <c r="E919" s="3" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="920" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B920" s="10">
+        <v>45859</v>
+      </c>
+      <c r="C920" s="3" t="s">
+        <v>1931</v>
+      </c>
+      <c r="D920" s="7" t="s">
+        <v>1932</v>
+      </c>
+      <c r="E920" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="921" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B921" s="10">
+        <v>45859</v>
+      </c>
+      <c r="C921" s="3" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D921" s="7" t="s">
+        <v>1932</v>
+      </c>
+      <c r="E921" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="922" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B922" s="10">
+        <v>45860</v>
+      </c>
+      <c r="C922" s="3" t="s">
+        <v>1934</v>
+      </c>
+      <c r="D922" s="7" t="s">
+        <v>1935</v>
+      </c>
+      <c r="E922" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="923" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B923" s="10">
+        <v>45860</v>
+      </c>
+      <c r="C923" s="3" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D923" s="7" t="s">
+        <v>1935</v>
+      </c>
+      <c r="E923" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="924" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B924" s="10">
+        <v>45861</v>
+      </c>
+      <c r="C924" s="3" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D924" s="7" t="s">
+        <v>1937</v>
+      </c>
+      <c r="E924" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="925" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B925" s="10">
+        <v>45864</v>
+      </c>
+      <c r="C925" s="3" t="s">
+        <v>1942</v>
+      </c>
+      <c r="D925" s="7" t="s">
+        <v>1943</v>
+      </c>
+      <c r="E925" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="926" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B926" s="10">
+        <v>45864</v>
+      </c>
+      <c r="C926" s="3" t="s">
+        <v>1944</v>
+      </c>
+      <c r="D926" s="7" t="s">
+        <v>1945</v>
+      </c>
+      <c r="E926" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="927" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B927" s="10">
+        <v>45864</v>
+      </c>
+      <c r="C927" s="3" t="s">
+        <v>1946</v>
+      </c>
+      <c r="D927" s="7" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E927" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="928" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B928" s="10">
+        <v>45864</v>
+      </c>
+      <c r="C928" s="3" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D928" s="7" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E928" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="929" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B929" s="10">
+        <v>45864</v>
+      </c>
+      <c r="C929" s="3" t="s">
+        <v>1950</v>
+      </c>
+      <c r="D929" s="7" t="s">
+        <v>1951</v>
+      </c>
+      <c r="E929" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="930" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B930" s="10">
+        <v>45865</v>
+      </c>
+      <c r="C930" s="3" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D930" s="7" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E930" s="3" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="931" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B931" s="10">
+        <v>45865</v>
+      </c>
+      <c r="C931" s="3" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D931" s="7" t="s">
+        <v>1956</v>
+      </c>
+      <c r="E931" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="932" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B932" s="10">
+        <v>45866</v>
+      </c>
+      <c r="C932" s="3" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D932" s="7" t="s">
+        <v>1958</v>
+      </c>
+      <c r="E932" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="933" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B933" s="10">
+        <v>45866</v>
+      </c>
+      <c r="C933" s="3" t="s">
+        <v>1959</v>
+      </c>
+      <c r="D933" s="7" t="s">
+        <v>1960</v>
+      </c>
+      <c r="E933" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="934" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B934" s="5">
+        <v>45869</v>
+      </c>
+      <c r="C934" s="3" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D934" s="7" t="s">
+        <v>1962</v>
+      </c>
+      <c r="E934" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="935" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B935" s="5">
+        <v>45870</v>
+      </c>
+      <c r="C935" s="3" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D935" s="7" t="s">
+        <v>1964</v>
+      </c>
+      <c r="E935" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="936" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B936" s="5">
+        <v>45873</v>
+      </c>
+      <c r="C936" s="3" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D936" s="7" t="s">
+        <v>1970</v>
+      </c>
+      <c r="E936" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="937" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B937" s="5">
+        <v>45875</v>
+      </c>
+      <c r="C937" s="3" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D937" s="7" t="s">
+        <v>1966</v>
+      </c>
+      <c r="E937" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="938" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B938" s="5">
+        <v>45875</v>
+      </c>
+      <c r="C938" s="3" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D938" s="7" t="s">
+        <v>1968</v>
+      </c>
+      <c r="E938" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="939" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B939" s="5">
+        <v>45878</v>
+      </c>
+      <c r="C939" s="3" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D939" s="7" t="s">
+        <v>1972</v>
+      </c>
+      <c r="E939" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="940" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B940" s="5">
+        <v>45878</v>
+      </c>
+      <c r="C940" s="3" t="s">
+        <v>1973</v>
+      </c>
+      <c r="D940" s="7" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E940" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="941" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B941" s="5">
+        <v>45879</v>
+      </c>
+      <c r="C941" s="3" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D941" s="7" t="s">
+        <v>1976</v>
+      </c>
+      <c r="E941" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="942" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B942" s="5">
+        <v>45879</v>
+      </c>
+      <c r="C942" s="3" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D942" s="7" t="s">
+        <v>1983</v>
+      </c>
+      <c r="E942" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="943" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B943" s="5">
+        <v>45880</v>
+      </c>
+      <c r="C943" s="3" t="s">
+        <v>1977</v>
+      </c>
+      <c r="D943" s="7" t="s">
+        <v>1978</v>
+      </c>
+      <c r="E943" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="944" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B944" s="5">
+        <v>45880</v>
+      </c>
+      <c r="C944" s="3" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D944" s="7" t="s">
+        <v>1985</v>
+      </c>
+      <c r="E944" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="945" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B945" s="5">
+        <v>45881</v>
+      </c>
+      <c r="C945" s="3" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D945" s="7" t="s">
+        <v>1980</v>
+      </c>
+      <c r="E945" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="946" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B946" s="5">
+        <v>45881</v>
+      </c>
+      <c r="C946" s="3" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D946" s="7" t="s">
+        <v>1980</v>
+      </c>
+      <c r="E946" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="947" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B947" s="5">
+        <v>45882</v>
+      </c>
+      <c r="C947" s="3" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D947" s="7" t="s">
+        <v>1987</v>
+      </c>
+      <c r="E947" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="948" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B948" s="5">
+        <v>45883</v>
+      </c>
+      <c r="C948" s="3" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D948" s="7" t="s">
+        <v>1989</v>
+      </c>
+      <c r="E948" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="949" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B949" s="5">
+        <v>45884</v>
+      </c>
+      <c r="C949" s="3" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D949" s="7" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E949" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="950" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B950" s="5">
+        <v>45884</v>
+      </c>
+      <c r="C950" s="3" t="s">
+        <v>1994</v>
+      </c>
+      <c r="D950" s="7" t="s">
+        <v>1995</v>
+      </c>
+      <c r="E950" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="951" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B951" s="5">
+        <v>45886</v>
+      </c>
+      <c r="C951" s="3" t="s">
+        <v>1996</v>
+      </c>
+      <c r="D951" s="7" t="s">
+        <v>1997</v>
+      </c>
+      <c r="E951" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="952" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B952" s="5">
+        <v>45889</v>
+      </c>
+      <c r="C952" s="3" t="s">
+        <v>1998</v>
+      </c>
+      <c r="D952" s="7" t="s">
+        <v>1999</v>
+      </c>
+      <c r="E952" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="953" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B953" s="5">
+        <v>45889</v>
+      </c>
+      <c r="C953" s="3" t="s">
+        <v>2000</v>
+      </c>
+      <c r="D953" s="7" t="s">
+        <v>1999</v>
+      </c>
+      <c r="E953" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="954" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B954" s="5">
+        <v>45889</v>
+      </c>
+      <c r="C954" s="3" t="s">
+        <v>2001</v>
+      </c>
+      <c r="D954" s="7" t="s">
+        <v>2002</v>
+      </c>
+      <c r="E954" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="955" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B955" s="5">
+        <v>45890</v>
+      </c>
+      <c r="C955" s="3" t="s">
+        <v>2003</v>
+      </c>
+      <c r="D955" s="7" t="s">
+        <v>2004</v>
+      </c>
+      <c r="E955" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="956" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B956" s="5">
+        <v>45890</v>
+      </c>
+      <c r="C956" s="3" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D956" s="7" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E956" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="957" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B957" s="5">
+        <v>45890</v>
+      </c>
+      <c r="C957" s="3" t="s">
+        <v>2007</v>
+      </c>
+      <c r="D957" s="7" t="s">
+        <v>2008</v>
+      </c>
+      <c r="E957" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="958" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B958" s="5">
+        <v>45891</v>
+      </c>
+      <c r="C958" s="3" t="s">
+        <v>2009</v>
+      </c>
+      <c r="D958" s="7" t="s">
+        <v>2010</v>
+      </c>
+      <c r="E958" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="959" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B959" s="5">
+        <v>45894</v>
+      </c>
+      <c r="C959" s="3" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D959" s="7" t="s">
+        <v>2012</v>
+      </c>
+      <c r="E959" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="960" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B960" s="5">
+        <v>45894</v>
+      </c>
+      <c r="C960" s="3" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D960" s="7" t="s">
+        <v>2012</v>
+      </c>
+      <c r="E960" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="961" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B961" s="5">
+        <v>45894</v>
+      </c>
+      <c r="C961" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D961" s="7" t="s">
+        <v>2022</v>
+      </c>
+      <c r="E961" s="3" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="962" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B962" s="5">
+        <v>45895</v>
+      </c>
+      <c r="C962" s="3" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D962" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E962" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="963" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B963" s="5">
+        <v>45895</v>
+      </c>
+      <c r="C963" s="3" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D963" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E963" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="964" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B964" s="5">
+        <v>45896</v>
+      </c>
+      <c r="C964" s="3" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D964" s="7" t="s">
+        <v>2018</v>
+      </c>
+      <c r="E964" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="965" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B965" s="5">
+        <v>45897</v>
+      </c>
+      <c r="C965" s="3" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D965" s="7" t="s">
+        <v>2020</v>
+      </c>
+      <c r="E965" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="966" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B966" s="5">
+        <v>45898</v>
+      </c>
+      <c r="C966" s="3" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D966" s="7" t="s">
+        <v>2027</v>
+      </c>
+      <c r="E966" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="967" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B967" s="5">
+        <v>45900</v>
+      </c>
+      <c r="C967" s="3" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D967" s="7" t="s">
+        <v>2025</v>
+      </c>
+      <c r="E967" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="968" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="977" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="978" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="979" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -19646,6 +20604,12 @@
     <row r="982" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="983" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="984" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Videos that I watched.xlsx
+++ b/Videos that I watched.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a960143ed076ae3/Desktop/Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1219" documentId="13_ncr:1_{7A07CC95-52CD-48B0-A787-62FFE8F667E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09FB15BB-A0C4-4890-9CB7-4368322438C3}"/>
+  <xr:revisionPtr revIDLastSave="1380" documentId="13_ncr:1_{7A07CC95-52CD-48B0-A787-62FFE8F667E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEA004E8-ECB1-463B-AF9A-2B416B381AE7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1830" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2895" uniqueCount="2028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3003" uniqueCount="2098">
   <si>
     <t>Date</t>
   </si>
@@ -6697,6 +6697,216 @@
   </si>
   <si>
     <t xml:space="preserve"> Yang Berhenti Menteri Episod 11 | Merdeka Dahulu, Merdeka Sekarang </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=aqaqOeiaC7I</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nuclear Energy's Price, Urban Renewal, and Gig Worker Protection | Episode 74 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mHYf-ZPm_hY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ep 36 | Kisah sebenar pertambahan kerusi DUN Sarawak </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=B7onv32i3xA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Shifting gears: Malaysia bets on indigenous plant for EV future • FRANCE 24 English </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=CdlOwcL7hDc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (LIVE) Rafizi Ramli : Podcast YBM 19/09/25 - Episod 14 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=aTh9Rp_RAlg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ep 38 | Armizan: "Calon Ketua Menteri Sabah terbaik adalah..." </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Pl0-cl__bFE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [LANGSUNG] Visual langsung misi Global Sumud Flotilla | 30 Sept 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=XIsA3D_9LB4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ribuan demo desak bebas aktivis! Wakil kedutaan AS enggan keluar </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Ss9L1YS_zT0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Malam tadi kita malukan Abah', Armada gesa pulih maruah Muhyiddin </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PQcYMWNqn5E</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Suasana Perhimpunan Agung Tahunan Bersatu bertukar kecoh </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=117-B-KIddI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 6 Oktober 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=J2raNxZ8L1E</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 7 Oktober 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=UY-S6OPFKLY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=61qTIbWeALc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [LANGSUNG] Ketibaan 23 delegasi GSF Malaysia di KLIA | 7 Okt 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=k_j2tL0gdw0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EP7 #KenaSoal | Halatuju MUDA, 263 Cybertrooper, Kontroversi MOTAC, Elaun YB, Budi95, Misi GSF </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=9rqOW-WLTwQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 8 Oktober 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=WZJLjtUVww8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Belanjawan 2026 Malaysia MADANI | 10 Oktober 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=FV1DGv-EDYM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Yang Berhenti Menteri Episod 17 — Belanjawan 2026, Janji &amp; FAM </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Bw1j1mFxrqQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> S02E04 | Dun Sabah Bubar, Cerita Itu Ini Parti Politik di Sabah </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ITHQT-TVky8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 13 Oktober 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gMfzTuPbUjU</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0cZxPqcabQM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 14 Oktober 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hvMgQFmLYGY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Kes menjadi-jadi di sekolah, KPM perlu tegas!' - Syed Saddiq </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=x3Aa6UNX7u4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 15 Oktober 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=WRrbUcwxUPk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> My daughter was stabbed 200 times, mum of Bandar Utama victim claims </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=oi27wjE598c</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Aduan Rakyat Yang Buat Saya Serba Salah </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=qr57JzGywys</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HADI AWANG Gesa Kerajaan Hidupkan Usaha Guna Dinar, Begini Reaksi Rafizi Ramli! </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=05pLKN0DAig</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'My daughter was stabbed 200 times', heartbroken mother says, urging an end to fake stories </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=UF0gzojeXb4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 16 Oktober 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VkR92Hsn09o</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (PRN Sabah) Sidang Media Penyertaan Ahli PKR &amp; Ahli Parti PBS Ke Parti Warisan </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=m9Ga7seOKyc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Edisi Siasat papar video bos PBS dan Albert bincang soal duit </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KbbtwFgvTmw</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Yang Berhenti Menteri Episod 18 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=a96r_PinYjo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Timbalan Presiden PBS pula terkait dakwaan rasuah Sabah </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=6E1Ut2OAvtw</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 22 Oktober 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=_jJwg-EenLM&amp;lc=UgywaxhLuA1d-vdLZ8J4AaABAg.AOXvRo6d1GOAO_dWfSDmNT</t>
+  </si>
+  <si>
+    <t>EPISOD 15: BAHAGIAN 1: MEMBONGKAR ISU MINERAL SABAH BERSAMA BERSAMA DATO' ALBERT TEI</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=wpsdrVjcsSQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 23 Oktober 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=dwCMrcbJiXo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> S02E05 | 40%, denda 100 juta, cerita politik Sabah </t>
   </si>
 </sst>
 </file>
@@ -7074,7 +7284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:E990"/>
+  <dimension ref="B3:E1120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" style="5" customWidth="1"/>
@@ -20575,41 +20785,639 @@
     </row>
     <row r="967" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B967" s="5">
+        <v>45899</v>
+      </c>
+      <c r="C967" s="3" t="s">
+        <v>2028</v>
+      </c>
+      <c r="D967" s="7" t="s">
+        <v>2029</v>
+      </c>
+      <c r="E967" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="968" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B968" s="5">
         <v>45900</v>
       </c>
-      <c r="C967" s="3" t="s">
+      <c r="C968" s="3" t="s">
         <v>2024</v>
       </c>
-      <c r="D967" s="7" t="s">
+      <c r="D968" s="7" t="s">
         <v>2025</v>
       </c>
-      <c r="E967" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="968" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="E968" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="969" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B969" s="10">
+        <v>45906</v>
+      </c>
+      <c r="C969" s="3" t="s">
+        <v>2044</v>
+      </c>
+      <c r="D969" s="7" t="s">
+        <v>2045</v>
+      </c>
+      <c r="E969" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="970" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B970" s="10">
+        <v>45907</v>
+      </c>
+      <c r="C970" s="3" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D970" s="7" t="s">
+        <v>2043</v>
+      </c>
+      <c r="E970" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="971" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B971" s="5">
+        <v>45915</v>
+      </c>
+      <c r="C971" s="3" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D971" s="7" t="s">
+        <v>2031</v>
+      </c>
+      <c r="E971" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="972" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B972" s="5">
+        <v>45918</v>
+      </c>
+      <c r="C972" s="3" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D972" s="7" t="s">
+        <v>2033</v>
+      </c>
+      <c r="E972" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="973" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B973" s="5">
+        <v>45919</v>
+      </c>
+      <c r="C973" s="3" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D973" s="7" t="s">
+        <v>2035</v>
+      </c>
+      <c r="E973" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="974" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B974" s="5">
+        <v>45922</v>
+      </c>
+      <c r="C974" s="3" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D974" s="7" t="s">
+        <v>2037</v>
+      </c>
+      <c r="E974" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="975" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B975" s="5">
+        <v>45930</v>
+      </c>
+      <c r="C975" s="3" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D975" s="7" t="s">
+        <v>2039</v>
+      </c>
+      <c r="E975" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="976" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B976" s="5">
+        <v>45932</v>
+      </c>
+      <c r="C976" s="3" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D976" s="7" t="s">
+        <v>2041</v>
+      </c>
+      <c r="E976" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="977" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B977" s="5">
+        <v>45936</v>
+      </c>
+      <c r="C977" s="3" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D977" s="7" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E977" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="978" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B978" s="5">
+        <v>45936</v>
+      </c>
+      <c r="C978" s="3" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D978" s="7" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E978" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="979" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B979" s="5">
+        <v>45937</v>
+      </c>
+      <c r="C979" s="3" t="s">
+        <v>2048</v>
+      </c>
+      <c r="D979" s="7" t="s">
+        <v>2049</v>
+      </c>
+      <c r="E979" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="980" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B980" s="5">
+        <v>45937</v>
+      </c>
+      <c r="C980" s="3" t="s">
+        <v>2050</v>
+      </c>
+      <c r="D980" s="7" t="s">
+        <v>2049</v>
+      </c>
+      <c r="E980" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="981" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B981" s="5">
+        <v>45937</v>
+      </c>
+      <c r="C981" s="3" t="s">
+        <v>2051</v>
+      </c>
+      <c r="D981" s="7" t="s">
+        <v>2052</v>
+      </c>
+      <c r="E981" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="982" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B982" s="5">
+        <v>45938</v>
+      </c>
+      <c r="C982" s="3" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D982" s="7" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E982" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="983" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B983" s="5">
+        <v>45940</v>
+      </c>
+      <c r="C983" s="3" t="s">
+        <v>2057</v>
+      </c>
+      <c r="D983" s="7" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E983" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="984" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B984" s="5">
+        <v>45940</v>
+      </c>
+      <c r="C984" s="3" t="s">
+        <v>2059</v>
+      </c>
+      <c r="D984" s="7" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E984" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="985" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B985" s="5">
+        <v>45942</v>
+      </c>
+      <c r="C985" s="3" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D985" s="7" t="s">
+        <v>2062</v>
+      </c>
+      <c r="E985" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="986" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B986" s="5">
+        <v>45943</v>
+      </c>
+      <c r="C986" s="3" t="s">
+        <v>2063</v>
+      </c>
+      <c r="D986" s="7" t="s">
+        <v>2064</v>
+      </c>
+      <c r="E986" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="987" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B987" s="5">
+        <v>45943</v>
+      </c>
+      <c r="C987" s="3" t="s">
+        <v>2065</v>
+      </c>
+      <c r="D987" s="7" t="s">
+        <v>2064</v>
+      </c>
+      <c r="E987" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="988" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B988" s="5">
+        <v>45944</v>
+      </c>
+      <c r="C988" s="3" t="s">
+        <v>2066</v>
+      </c>
+      <c r="D988" s="7" t="s">
+        <v>2067</v>
+      </c>
+      <c r="E988" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="989" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B989" s="5">
+        <v>45944</v>
+      </c>
+      <c r="C989" s="3" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D989" s="7" t="s">
+        <v>2069</v>
+      </c>
+      <c r="E989" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="990" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B990" s="5">
+        <v>45944</v>
+      </c>
+      <c r="C990" s="3" t="s">
+        <v>2074</v>
+      </c>
+      <c r="D990" s="7" t="s">
+        <v>2075</v>
+      </c>
+      <c r="E990" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="991" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B991" s="5">
+        <v>45945</v>
+      </c>
+      <c r="C991" s="3" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D991" s="7" t="s">
+        <v>2071</v>
+      </c>
+      <c r="E991" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="992" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B992" s="5">
+        <v>45945</v>
+      </c>
+      <c r="C992" s="3" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D992" s="7" t="s">
+        <v>2077</v>
+      </c>
+      <c r="E992" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="993" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B993" s="5">
+        <v>45946</v>
+      </c>
+      <c r="C993" s="3" t="s">
+        <v>2072</v>
+      </c>
+      <c r="D993" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="E993" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="994" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B994" s="5">
+        <v>45946</v>
+      </c>
+      <c r="C994" s="3" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D994" s="7" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E994" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="995" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B995" s="5">
+        <v>45946</v>
+      </c>
+      <c r="C995" s="3" t="s">
+        <v>2080</v>
+      </c>
+      <c r="D995" s="7" t="s">
+        <v>2081</v>
+      </c>
+      <c r="E995" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="996" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B996" s="5">
+        <v>45947</v>
+      </c>
+      <c r="C996" s="3" t="s">
+        <v>2082</v>
+      </c>
+      <c r="D996" s="7" t="s">
+        <v>2083</v>
+      </c>
+      <c r="E996" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="997" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B997" s="5">
+        <v>45947</v>
+      </c>
+      <c r="C997" s="3" t="s">
+        <v>2086</v>
+      </c>
+      <c r="D997" s="7" t="s">
+        <v>2087</v>
+      </c>
+      <c r="E997" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="998" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B998" s="10">
+        <v>45948</v>
+      </c>
+      <c r="C998" t="s">
+        <v>2084</v>
+      </c>
+      <c r="D998" s="7" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E998" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="999" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B999" s="10">
+        <v>45951</v>
+      </c>
+      <c r="C999" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="D999" s="7" t="s">
+        <v>2089</v>
+      </c>
+      <c r="E999" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1000" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1000" s="10">
+        <v>45952</v>
+      </c>
+      <c r="C1000" s="3" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D1000" s="7" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1000" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1001" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1001" s="10">
+        <v>45952</v>
+      </c>
+      <c r="C1001" s="3" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1001" s="7" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E1001" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1002" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1002" s="10">
+        <v>45953</v>
+      </c>
+      <c r="C1002" s="3" t="s">
+        <v>2092</v>
+      </c>
+      <c r="D1002" s="7" t="s">
+        <v>2093</v>
+      </c>
+      <c r="E1002" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1003" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1003" s="10">
+        <v>45953</v>
+      </c>
+      <c r="C1003" s="3" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D1003" s="7" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E1003" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1004" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1005" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1006" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1007" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1008" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1009" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1010" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1011" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1012" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1013" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1014" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1015" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1016" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1017" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1018" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1019" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1020" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1021" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1022" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1023" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1024" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1025" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1026" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1027" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1028" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1029" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1030" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1031" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1032" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1033" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1034" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1035" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1036" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1037" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1038" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1039" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1040" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1041" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1042" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1043" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1044" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1045" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1046" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1047" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1048" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1049" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1050" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1051" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1052" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1053" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1054" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1055" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1056" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1057" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1058" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1059" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1060" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1061" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1062" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1063" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1064" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1065" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1066" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1067" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1068" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1069" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1070" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1071" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1072" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1073" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1074" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1075" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1076" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1077" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1078" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1079" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1080" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1081" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1082" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1083" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1084" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1085" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1086" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1087" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1088" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1089" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1090" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1091" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1092" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1093" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1094" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1095" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1096" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1097" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1098" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1099" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1100" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1101" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1102" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1103" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1104" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1105" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1106" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1107" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1108" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1109" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1110" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1111" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1112" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1113" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1114" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1115" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1116" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1117" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1118" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1119" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1120" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Videos that I watched.xlsx
+++ b/Videos that I watched.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a960143ed076ae3/Desktop/Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1380" documentId="13_ncr:1_{7A07CC95-52CD-48B0-A787-62FFE8F667E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEA004E8-ECB1-463B-AF9A-2B416B381AE7}"/>
+  <xr:revisionPtr revIDLastSave="1916" documentId="13_ncr:1_{7A07CC95-52CD-48B0-A787-62FFE8F667E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29D29425-7C48-41C8-B6E4-3BF78DA1055B}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1830" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1830" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3003" uniqueCount="2098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3249" uniqueCount="2262">
   <si>
     <t>Date</t>
   </si>
@@ -6907,6 +6908,512 @@
   </si>
   <si>
     <t xml:space="preserve"> S02E05 | 40%, denda 100 juta, cerita politik Sabah </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=NVoXfMg1uIo</t>
+  </si>
+  <si>
+    <t>Kisah Sebenar: Wan Ahmad Fayhsal &amp; Krisis Dalam Bersatu | THE ZAID IBRAHIM PODCAST</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=CnMTDwpoUe4</t>
+  </si>
+  <si>
+    <t>Trick Lama: Dua Singa, Satu Gunung: Wan Fayhsal &amp; Wan Saiful Bersuara Tentang Perang Saudara Bersatu</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LywrHwKyuqk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ep 45 | Reformasi: Satu langkah ke depan, dua ke belakang? </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Trick Lama: Dua Singa, Satu Gunung: Wan Fayhsal &amp; Wan Saiful Bersuara Tentang Perang Saudara Bersatu </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gIWnMN1PBWs</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 27 Oktober 2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EP12 Rafizi Kuat Merajuk? Cerita PKR, Isu Farhash - Bekas Menteri Jawab Semua! | Explain Sikit </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=cOscfi0Laf0&amp;t=221s</t>
+  </si>
+  <si>
+    <t>(https://youtu.be/cOscfi0Laf0?si=6ULHurprdej5NPg2&amp;t=2432)
+rafizi said he can bring this gov down. He can bring more mp than azmin</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=_ocHnR8GzdI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Trump praises Malaysian PM, ASEAN in fiery speech, says 'Everything you touch turns to Gold' </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3akve0LERBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 29 Oktober 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=eVFRvVDJ94A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ‘Malaysia Helped Stop the War’, Trump Praises Malaysian PM Anwar at APEC Summit | AC1G </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Soal Soalan yang semua orang nak tahu pasal hala tuju MUDA…👀 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/HsLoqvLd5Dk</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ckLVeI-GOWg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> S02E06 | 40%, UPKO tanding logo sendiri, PR nightmare </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=r1-jqmI7CMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 30 Oktober 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=qP2yPUJcJIc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Malaysian PM Anwar Ibrahim on how he's navigating Trump's tariffs | ABC NEWS </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=s0Bn8cr7gVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FLEXIMART DIBUKA!!! </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=RDKbmGS7TGI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 03 November 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=2ZP7q8AuXyo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 04 November 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=9z7z0CKlKYI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EP175 | Lawatan Rasmi Presiden AS, Perjanjian Timbal Balas Malaysia–AS, Perpecahan Dalaman BERSATU </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=7kSI03Tz77k</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Saya dah haramkan anak saya bermain Roblox' - Fahmi </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=sTyxmcGlQ84</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 06 November 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=2M8dKtWRHbQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Skandal Sabah: Video kaitkan Timbalan Presiden Star pula muncul </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=RdDtq_CVdzc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 🔴 MAJLIS PENGUMUMAN CALON KEADILAN PRU DEWAN UNDANGAN SABAH 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=bKXTxMX2EFM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 10 November 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mXM3xvvJHHQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [Video Penuh] Ucapan Mohamad Sabu di Konvensyen Nasional 2025 Parti Amanah Negara </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=t4PrnmQFYRc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 12 November 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=CROnfxELvk4</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=grx0cAi0eQ8</t>
+  </si>
+  <si>
+    <t>Dari Reformasi, Ke Reformanan, Kini Reformusa</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=6gLbeFqD6WU</t>
+  </si>
+  <si>
+    <t>Pendedahan terbaru Tei: 'Duit beli kereta, kedai'</t>
+  </si>
+  <si>
+    <t>https://www.reddit.com/r/malaysia/comments/1owy1h9/pmx_caught_stealing_from_the_rakyat/</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMX caught stealing from the rakyat </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=rZGKqzJDJ8c</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> #82 | Behind The Trump Negotiation (Tengku Zafrul Aziz) </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VQGvUuqT86g</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 13 November 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=cQ0AhxxJ_9s</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Kenapa PKR? Kenapa Ampang? </t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@keadilan.putatan/live?search_type=live&amp;search_id=2025111508243002F482AD3C4D1531F74F&amp;search_keyword=sabah%20penamaan%20calon&amp;enter_from_merge=search_result&amp;enter_method=live_cell&amp;search_result_id=7572733208167009044</t>
+  </si>
+  <si>
+    <t>sabah penamaan calon</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ZqYX_gNpTlE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [LANGSUNG] Sabah Memilih: Hari Penamaan Calon PRN Sabah ke-17 | 15 Nov 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=CpdkrYW5Tgw</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (LANGSUNG) Siaran Khas Pembentangan Belanjawan Selangor 2026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rafizi Jual Nasi Bawah RM5 &amp; Dinamik PRN Sabah | YBM EP 22 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=K_3PkyGlPG8</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Dc8HescuPgI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 17 November 2025 </t>
+  </si>
+  <si>
+    <t>https://www.reddit.com/r/Bolehland/comments/1oyknbq/unc_got_mad_in_whatsapp_group_chat/</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Unc got mad in WhatsApp group chat 🤣🤣 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=x68u59WdB60</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EP178 | ART 2025, Haluan Baharu Tengku Zafrul, Langkah Selepas Tamat Senator </t>
+  </si>
+  <si>
+    <t>tengku zafrul nak masuk pkr sebab dia tak ngam dgn umno. Tak sekepala dgn diorng. He admit he has royal connection but other connection are also necessary to be in power.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PKrTA22l7xI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 18 November 2025 </t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/watch/?v=836443699094605</t>
+  </si>
+  <si>
+    <t>Kami tenang-tenang sahaja.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=cHfLVPIR9Fc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> S02E10: Penamaan calon dan roti gardenia </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=E0e6jLkTp2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 20 November 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=IWkgNs8WgG4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 19 November 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=sTHk4KP8TEs</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EP179 | Amirudin Bakal Menteri Kabinet?, Perpecahan Dalaman PKR, Belanjawan 2026, Konsesi Parkir </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Fm_IPGd79IA</t>
+  </si>
+  <si>
+    <t>EP25 - Sabah’s Big Test: National Party Vision vs the 40% Reality</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ool9LNk4Flg</t>
+  </si>
+  <si>
+    <t>THE ROUNDTABLE: 2025 SABAH ELECTION EDITION — FULL DISCUSSION</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=TcrbumHdyDM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dolla meets with Fahmi at Parliament </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=nLHe8EL_V_o</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 25 November 2025 </t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/17WxvkZwtz/</t>
+  </si>
+  <si>
+    <t>JUST IN 🔥: Rupa-rupanya dalang di sebalik rakaman video skandal rasuah Sabah adalah Anwar Ibrahim.
+Tahniah kepada para pemimpin politik Gabungan Rasuah Sabah (GRS) yang telah diperangkap oleh PMX.</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1DKe1c2AYC/</t>
+  </si>
+  <si>
+    <t>PANAS 🔥: Bila kata dakwaan rasuah RM629,000 berhubung Shamsul Iskandar adalah “Tohmahan”, selepas tengok video ini baru kita faham. Bayangkan betapa menakutkan keadaan sekarang</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=tvkJ5EynhCc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 26 November 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=APE5lxWZqPU</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 27 November 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=osncDf8XElE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Albert Tei ditahan pegawai SPRM dan dihantar semula beberapa minit kemudian </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=4peWiVlo3wE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SPRM Tahan Tiga Individu Utama Dalam Kes Dakwaan Rasuah Libatkan Bekas Setiausaha Politik Kanan PM </t>
+  </si>
+  <si>
+    <t>fuck you</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=pGdNql7Ovz4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Shamsul Iskandar vs Albert Tei, Bencana Banjir &amp; Izzah MB Selangor? - YBM EP 24 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=CErs6dsPmlo</t>
+  </si>
+  <si>
+    <t>Living the nightmare: homeless man outside bank tells his story</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VK4rR299IzI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [LANGSUNG] #SabahMemilih2025 | Analisis komprehensif Hari Pengundian | 29 November 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=DYq-ug3tL2s</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (PRN Sabah) Keputusan "Tidak Rasmi" PRN Sabah 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Rjn3Uac55FY</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@bernamaofficial/live?search_type=live&amp;search_id=2025112920205813DB8AD550B305BDCBB5&amp;search_keyword=sabah&amp;enter_from_merge=search_result&amp;enter_method=live_cell&amp;search_result_id=7578110383301692168</t>
+  </si>
+  <si>
+    <t>BERNAMA Sabah election</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=BG82vh1ATlo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [LANGSUNG] #SabahMemilih2025 | Analisis Pasca Pilihan Raya Negeri Sabah ke-17 | 8AM | 30 Nov 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-UzoC3GepYk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [TERKINI] PRN Sabah: Hajiji angkat sumpah Ketua Menteri Sabah Ke-17 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=SsNPP6ruDDM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [TERKINI] Sidang media parti Warisan pasca PRN Sabah ke-17 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(https://youtu.be/sTHk4KP8TEs?si=GH38Vpa7LgCTnWM0&amp;t=4267)
+pkr election 2025  - it seems that rafizi said something along the lines of  "baik saya tak bertanding(timbalan presiden PKR)
+(https://youtu.be/sTHk4KP8TEs?si=jX0KGr_E1122CTJr&amp;t=4255)
+the reason izzah contest timbalan president pkr - vague sangat
+(https://youtu.be/sTHk4KP8TEs?si=AW23V9CQT1CC9jS9&amp;t=5276) and (https://www.youtube.com/watch?v=2Lxmeg1XBAg)
+rafizi and KJ says somewhat the same thing where amirudin masuk dalam menteri cabinet and izzah letak selangor mb
+</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=IoczLnqc-D8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 1 Disember 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hN4BUDw4U-E</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/17k4hndUmg/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ada lagi sambungan video rupanya. Kali ini di pautan https://vt.tiktok.com/ZSfbwMMD4/
+Ini menyambung isu surat sokongan yang saya bangkitkan di Parlimen dua minggu lepas. Kali ini wanita ini mendakwa bahawa PMX sendiri yang arah Setpolnya sain surat sokongan itu.
+Nah,kalau PMX kata setpolnya resign kerana prinsip dan integriti, kali ini siapa yang kena resign? Siapa yang nak kena buat siasatan ni? Dan knp dalam parlimen PMX kata dia sudah buat 'teguran keras' kpd setpol kerana tulis surat ini?
+Inilah budaya baru </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=WBXFplbyapc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 2 Disember 2025 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=8I5yuRy_GHM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PRN Sabah: PKR Terkubur? Masa Depan PH | YBM EP 25 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=WnOba7sHugI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LANGSUNG: Persidangan Dewan Rakyat | Mesyuarat Ketiga Penggal Keempat | 4 Disember 2025 </t>
+  </si>
+  <si>
+    <t>https://www.reddit.com/r/Malacca/comments/1pdp1fa/onetwothree_gunshots_chilling_audio_clip_of/</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'One...two...three, gunshots': Chilling audio clip of unfinished phone call during police op points to trio's cold-blooded murder </t>
+  </si>
+  <si>
+    <t>https://x.com/jasonyew/status/1998651578430149000</t>
+  </si>
+  <si>
+    <t>"Mungkin tahun depan tamat perkhidmatan saya, sudah 3 kali sambung, @rafiziramli
+ pun tak suka dengan saya." - Azam Baki</t>
+  </si>
+  <si>
+    <t>https://x.com/akmalnasir/status/1998342231778816505</t>
+  </si>
+  <si>
+    <t>Ramai tak perasan, akhirnya Kelantan akan dapat TAPS/empangan pertama, kita bina di Machang ‼️
+Setakat ni dah 3 kali saya &amp; team turun untuk push pengambilan tanah dipercepatkan 🏃 🏃
+Kita akan terus gasak dan desak pastikan projek berjalan sehingga siap 👊🏻👊🏻👊🏻</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=xhBieNkwYjw</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [SINAR LIVE] Sidang media ketua-ketua bahagian Bersatu Negeri Perak </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=_ZTXxHcvjDk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> E-invois, SST &amp; LHDN: Bila Kutip Cukai Jadi Beban </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Rn3_ltxtW-k</t>
+  </si>
+  <si>
+    <t>Pengumuman khas Kabinet Kerajaan MADANI.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=UDyqU87cWXU</t>
+  </si>
+  <si>
+    <t>Reformasi Bukan Content: Azam Baki, UEC &amp; Felda | YBM EP 26</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=IwbZMk9vk4s</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ep 61 | ⁠Rombakan Kabinet; puas hati atau sakit hati? </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=aIFlu97t6Gk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Court ruling on Najib reduces Malay rulers' powers, will appeal - Shafee </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=fv5XTIE5dWI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Eps Hang Nadim - Rejuvenasi Politik &amp; Masa Depan Negara |JPOS5E6 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=W5gI93CKvl0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rombakan Kabinet: Vaksin atau Panadol? | Bersatu Bergolak, PRU16 Makin Kabur | YBM #27 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=CcEryIGLnlg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Episod Terakhir 2025: 10 Perkara Yang Kita Tak Boleh Buat-buat Lupa | YBM #28 </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=iIftO-nh4sQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hari Tu Pasal Akmal, Hari Ni Syed Ibrahim </t>
   </si>
 </sst>
 </file>
@@ -7015,10 +7522,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7284,7 +7787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:E1120"/>
+  <dimension ref="B3:E1125"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" style="5" customWidth="1"/>
@@ -19847,13 +20350,13 @@
     </row>
     <row r="900" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B900" s="5">
-        <v>45818</v>
+        <v>45816</v>
       </c>
       <c r="C900" s="3" t="s">
-        <v>1888</v>
+        <v>2117</v>
       </c>
       <c r="D900" s="7" t="s">
-        <v>1889</v>
+        <v>2116</v>
       </c>
       <c r="E900" s="3" t="s">
         <v>5</v>
@@ -19861,13 +20364,13 @@
     </row>
     <row r="901" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B901" s="5">
-        <v>45828</v>
+        <v>45818</v>
       </c>
       <c r="C901" s="3" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="D901" s="7" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="E901" s="3" t="s">
         <v>5</v>
@@ -19875,13 +20378,13 @@
     </row>
     <row r="902" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B902" s="5">
-        <v>45830</v>
+        <v>45828</v>
       </c>
       <c r="C902" s="3" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="D902" s="7" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="E902" s="3" t="s">
         <v>5</v>
@@ -19889,13 +20392,13 @@
     </row>
     <row r="903" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B903" s="5">
-        <v>45832</v>
+        <v>45830</v>
       </c>
       <c r="C903" s="3" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="D903" s="7" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="E903" s="3" t="s">
         <v>5</v>
@@ -19903,13 +20406,13 @@
     </row>
     <row r="904" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B904" s="5">
-        <v>45836</v>
+        <v>45832</v>
       </c>
       <c r="C904" s="3" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="D904" s="7" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="E904" s="3" t="s">
         <v>5</v>
@@ -19917,13 +20420,13 @@
     </row>
     <row r="905" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B905" s="5">
-        <v>45839</v>
+        <v>45836</v>
       </c>
       <c r="C905" s="3" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="D905" s="7" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="E905" s="3" t="s">
         <v>5</v>
@@ -19934,10 +20437,10 @@
         <v>45839</v>
       </c>
       <c r="C906" s="3" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="D906" s="7" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="E906" s="3" t="s">
         <v>5</v>
@@ -19945,41 +20448,41 @@
     </row>
     <row r="907" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B907" s="5">
-        <v>45842</v>
+        <v>45839</v>
       </c>
       <c r="C907" s="3" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="D907" s="7" t="s">
-        <v>1903</v>
-      </c>
-      <c r="E907" s="7" t="s">
-        <v>1906</v>
+        <v>1901</v>
+      </c>
+      <c r="E907" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="908" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B908" s="5">
-        <v>45843</v>
+        <v>45842</v>
       </c>
       <c r="C908" s="3" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="D908" s="7" t="s">
-        <v>1905</v>
-      </c>
-      <c r="E908" s="3" t="s">
-        <v>5</v>
+        <v>1903</v>
+      </c>
+      <c r="E908" s="7" t="s">
+        <v>1906</v>
       </c>
     </row>
     <row r="909" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B909" s="5">
-        <v>45844</v>
+        <v>45843</v>
       </c>
       <c r="C909" s="3" t="s">
-        <v>1919</v>
+        <v>1904</v>
       </c>
       <c r="D909" s="7" t="s">
-        <v>1920</v>
+        <v>1905</v>
       </c>
       <c r="E909" s="3" t="s">
         <v>5</v>
@@ -19987,13 +20490,13 @@
     </row>
     <row r="910" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B910" s="5">
-        <v>45845</v>
+        <v>45844</v>
       </c>
       <c r="C910" s="3" t="s">
-        <v>1909</v>
+        <v>1919</v>
       </c>
       <c r="D910" s="7" t="s">
-        <v>1910</v>
+        <v>1920</v>
       </c>
       <c r="E910" s="3" t="s">
         <v>5</v>
@@ -20001,13 +20504,13 @@
     </row>
     <row r="911" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B911" s="5">
-        <v>45849</v>
+        <v>45845</v>
       </c>
       <c r="C911" s="3" t="s">
-        <v>1915</v>
+        <v>1909</v>
       </c>
       <c r="D911" s="7" t="s">
-        <v>1916</v>
+        <v>1910</v>
       </c>
       <c r="E911" s="3" t="s">
         <v>5</v>
@@ -20015,13 +20518,13 @@
     </row>
     <row r="912" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B912" s="5">
-        <v>45850</v>
+        <v>45849</v>
       </c>
       <c r="C912" s="3" t="s">
-        <v>1911</v>
+        <v>1915</v>
       </c>
       <c r="D912" s="7" t="s">
-        <v>1912</v>
+        <v>1916</v>
       </c>
       <c r="E912" s="3" t="s">
         <v>5</v>
@@ -20029,13 +20532,13 @@
     </row>
     <row r="913" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B913" s="5">
-        <v>45851</v>
+        <v>45850</v>
       </c>
       <c r="C913" s="3" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="D913" s="7" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="E913" s="3" t="s">
         <v>5</v>
@@ -20046,10 +20549,10 @@
         <v>45851</v>
       </c>
       <c r="C914" s="3" t="s">
-        <v>1917</v>
+        <v>1913</v>
       </c>
       <c r="D914" s="7" t="s">
-        <v>1918</v>
+        <v>1914</v>
       </c>
       <c r="E914" s="3" t="s">
         <v>5</v>
@@ -20060,27 +20563,27 @@
         <v>45851</v>
       </c>
       <c r="C915" s="3" t="s">
-        <v>1927</v>
+        <v>1917</v>
       </c>
       <c r="D915" s="7" t="s">
-        <v>1928</v>
+        <v>1918</v>
       </c>
       <c r="E915" s="3" t="s">
-        <v>1930</v>
+        <v>5</v>
       </c>
     </row>
     <row r="916" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B916" s="5">
-        <v>45852</v>
+        <v>45851</v>
       </c>
       <c r="C916" s="3" t="s">
-        <v>1921</v>
+        <v>1927</v>
       </c>
       <c r="D916" s="7" t="s">
-        <v>1922</v>
+        <v>1928</v>
       </c>
       <c r="E916" s="3" t="s">
-        <v>5</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="917" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -20088,10 +20591,10 @@
         <v>45852</v>
       </c>
       <c r="C917" s="3" t="s">
-        <v>1925</v>
+        <v>1921</v>
       </c>
       <c r="D917" s="7" t="s">
-        <v>1926</v>
+        <v>1922</v>
       </c>
       <c r="E917" s="3" t="s">
         <v>5</v>
@@ -20099,44 +20602,44 @@
     </row>
     <row r="918" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B918" s="5">
-        <v>45853</v>
+        <v>45852</v>
       </c>
       <c r="C918" s="3" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="D918" s="7" t="s">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="E918" s="3" t="s">
-        <v>1929</v>
+        <v>5</v>
       </c>
     </row>
     <row r="919" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B919" s="5">
+        <v>45853</v>
+      </c>
+      <c r="C919" s="3" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D919" s="7" t="s">
+        <v>1924</v>
+      </c>
+      <c r="E919" s="3" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="920" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B920" s="5">
         <v>45856</v>
       </c>
-      <c r="C919" s="3" t="s">
+      <c r="C920" s="3" t="s">
         <v>1939</v>
       </c>
-      <c r="D919" s="7" t="s">
+      <c r="D920" s="7" t="s">
         <v>1940</v>
       </c>
-      <c r="E919" s="3" t="s">
+      <c r="E920" s="3" t="s">
         <v>1941</v>
-      </c>
-    </row>
-    <row r="920" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B920" s="10">
-        <v>45859</v>
-      </c>
-      <c r="C920" s="3" t="s">
-        <v>1931</v>
-      </c>
-      <c r="D920" s="7" t="s">
-        <v>1932</v>
-      </c>
-      <c r="E920" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="921" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -20144,7 +20647,7 @@
         <v>45859</v>
       </c>
       <c r="C921" s="3" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="D921" s="7" t="s">
         <v>1932</v>
@@ -20155,13 +20658,13 @@
     </row>
     <row r="922" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B922" s="10">
-        <v>45860</v>
+        <v>45859</v>
       </c>
       <c r="C922" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="D922" s="7" t="s">
-        <v>1935</v>
+        <v>1932</v>
       </c>
       <c r="E922" s="3" t="s">
         <v>5</v>
@@ -20172,7 +20675,7 @@
         <v>45860</v>
       </c>
       <c r="C923" s="3" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="D923" s="7" t="s">
         <v>1935</v>
@@ -20183,13 +20686,13 @@
     </row>
     <row r="924" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B924" s="10">
-        <v>45861</v>
+        <v>45860</v>
       </c>
       <c r="C924" s="3" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="D924" s="7" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="E924" s="3" t="s">
         <v>5</v>
@@ -20197,13 +20700,13 @@
     </row>
     <row r="925" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B925" s="10">
-        <v>45864</v>
+        <v>45861</v>
       </c>
       <c r="C925" s="3" t="s">
-        <v>1942</v>
+        <v>1938</v>
       </c>
       <c r="D925" s="7" t="s">
-        <v>1943</v>
+        <v>1937</v>
       </c>
       <c r="E925" s="3" t="s">
         <v>5</v>
@@ -20214,10 +20717,10 @@
         <v>45864</v>
       </c>
       <c r="C926" s="3" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="D926" s="7" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="E926" s="3" t="s">
         <v>5</v>
@@ -20228,10 +20731,10 @@
         <v>45864</v>
       </c>
       <c r="C927" s="3" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="D927" s="7" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="E927" s="3" t="s">
         <v>5</v>
@@ -20242,10 +20745,10 @@
         <v>45864</v>
       </c>
       <c r="C928" s="3" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="D928" s="7" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="E928" s="3" t="s">
         <v>5</v>
@@ -20256,10 +20759,10 @@
         <v>45864</v>
       </c>
       <c r="C929" s="3" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="D929" s="7" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="E929" s="3" t="s">
         <v>5</v>
@@ -20267,16 +20770,16 @@
     </row>
     <row r="930" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B930" s="10">
-        <v>45865</v>
+        <v>45864</v>
       </c>
       <c r="C930" s="3" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="D930" s="7" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="E930" s="3" t="s">
-        <v>1954</v>
+        <v>5</v>
       </c>
     </row>
     <row r="931" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -20284,24 +20787,24 @@
         <v>45865</v>
       </c>
       <c r="C931" s="3" t="s">
-        <v>1955</v>
+        <v>1952</v>
       </c>
       <c r="D931" s="7" t="s">
-        <v>1956</v>
+        <v>1953</v>
       </c>
       <c r="E931" s="3" t="s">
-        <v>5</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="932" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B932" s="10">
-        <v>45866</v>
+        <v>45865</v>
       </c>
       <c r="C932" s="3" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="D932" s="7" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="E932" s="3" t="s">
         <v>5</v>
@@ -20312,24 +20815,24 @@
         <v>45866</v>
       </c>
       <c r="C933" s="3" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D933" s="7" t="s">
+        <v>1958</v>
+      </c>
+      <c r="E933" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="934" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B934" s="10">
+        <v>45866</v>
+      </c>
+      <c r="C934" s="3" t="s">
         <v>1959</v>
       </c>
-      <c r="D933" s="7" t="s">
+      <c r="D934" s="7" t="s">
         <v>1960</v>
-      </c>
-      <c r="E933" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="934" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B934" s="5">
-        <v>45869</v>
-      </c>
-      <c r="C934" s="3" t="s">
-        <v>1961</v>
-      </c>
-      <c r="D934" s="7" t="s">
-        <v>1962</v>
       </c>
       <c r="E934" s="3" t="s">
         <v>5</v>
@@ -20337,13 +20840,13 @@
     </row>
     <row r="935" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B935" s="5">
-        <v>45870</v>
+        <v>45869</v>
       </c>
       <c r="C935" s="3" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="D935" s="7" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="E935" s="3" t="s">
         <v>5</v>
@@ -20351,13 +20854,13 @@
     </row>
     <row r="936" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B936" s="5">
-        <v>45873</v>
+        <v>45870</v>
       </c>
       <c r="C936" s="3" t="s">
-        <v>1969</v>
+        <v>1963</v>
       </c>
       <c r="D936" s="7" t="s">
-        <v>1970</v>
+        <v>1964</v>
       </c>
       <c r="E936" s="3" t="s">
         <v>5</v>
@@ -20365,13 +20868,13 @@
     </row>
     <row r="937" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B937" s="5">
-        <v>45875</v>
+        <v>45873</v>
       </c>
       <c r="C937" s="3" t="s">
-        <v>1965</v>
+        <v>1969</v>
       </c>
       <c r="D937" s="7" t="s">
-        <v>1966</v>
+        <v>1970</v>
       </c>
       <c r="E937" s="3" t="s">
         <v>5</v>
@@ -20382,10 +20885,10 @@
         <v>45875</v>
       </c>
       <c r="C938" s="3" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="D938" s="7" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="E938" s="3" t="s">
         <v>5</v>
@@ -20393,13 +20896,13 @@
     </row>
     <row r="939" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B939" s="5">
-        <v>45878</v>
+        <v>45875</v>
       </c>
       <c r="C939" s="3" t="s">
-        <v>1971</v>
+        <v>1967</v>
       </c>
       <c r="D939" s="7" t="s">
-        <v>1972</v>
+        <v>1968</v>
       </c>
       <c r="E939" s="3" t="s">
         <v>5</v>
@@ -20410,10 +20913,10 @@
         <v>45878</v>
       </c>
       <c r="C940" s="3" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="D940" s="7" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="E940" s="3" t="s">
         <v>5</v>
@@ -20421,13 +20924,13 @@
     </row>
     <row r="941" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B941" s="5">
-        <v>45879</v>
+        <v>45878</v>
       </c>
       <c r="C941" s="3" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="D941" s="7" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="E941" s="3" t="s">
         <v>5</v>
@@ -20438,10 +20941,10 @@
         <v>45879</v>
       </c>
       <c r="C942" s="3" t="s">
-        <v>1982</v>
+        <v>1975</v>
       </c>
       <c r="D942" s="7" t="s">
-        <v>1983</v>
+        <v>1976</v>
       </c>
       <c r="E942" s="3" t="s">
         <v>5</v>
@@ -20449,13 +20952,13 @@
     </row>
     <row r="943" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B943" s="5">
-        <v>45880</v>
+        <v>45879</v>
       </c>
       <c r="C943" s="3" t="s">
-        <v>1977</v>
+        <v>1982</v>
       </c>
       <c r="D943" s="7" t="s">
-        <v>1978</v>
+        <v>1983</v>
       </c>
       <c r="E943" s="3" t="s">
         <v>5</v>
@@ -20466,10 +20969,10 @@
         <v>45880</v>
       </c>
       <c r="C944" s="3" t="s">
-        <v>1984</v>
+        <v>1977</v>
       </c>
       <c r="D944" s="7" t="s">
-        <v>1985</v>
+        <v>1978</v>
       </c>
       <c r="E944" s="3" t="s">
         <v>5</v>
@@ -20477,13 +20980,13 @@
     </row>
     <row r="945" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B945" s="5">
-        <v>45881</v>
+        <v>45880</v>
       </c>
       <c r="C945" s="3" t="s">
-        <v>1981</v>
+        <v>1984</v>
       </c>
       <c r="D945" s="7" t="s">
-        <v>1980</v>
+        <v>1985</v>
       </c>
       <c r="E945" s="3" t="s">
         <v>5</v>
@@ -20494,7 +20997,7 @@
         <v>45881</v>
       </c>
       <c r="C946" s="3" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="D946" s="7" t="s">
         <v>1980</v>
@@ -20505,13 +21008,13 @@
     </row>
     <row r="947" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B947" s="5">
-        <v>45882</v>
+        <v>45881</v>
       </c>
       <c r="C947" s="3" t="s">
-        <v>1986</v>
+        <v>1979</v>
       </c>
       <c r="D947" s="7" t="s">
-        <v>1987</v>
+        <v>1980</v>
       </c>
       <c r="E947" s="3" t="s">
         <v>5</v>
@@ -20519,13 +21022,13 @@
     </row>
     <row r="948" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B948" s="5">
-        <v>45883</v>
+        <v>45882</v>
       </c>
       <c r="C948" s="3" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="D948" s="7" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="E948" s="3" t="s">
         <v>5</v>
@@ -20533,13 +21036,13 @@
     </row>
     <row r="949" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B949" s="5">
-        <v>45884</v>
+        <v>45883</v>
       </c>
       <c r="C949" s="3" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="D949" s="7" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="E949" s="3" t="s">
         <v>5</v>
@@ -20550,10 +21053,10 @@
         <v>45884</v>
       </c>
       <c r="C950" s="3" t="s">
-        <v>1994</v>
+        <v>1990</v>
       </c>
       <c r="D950" s="7" t="s">
-        <v>1995</v>
+        <v>1991</v>
       </c>
       <c r="E950" s="3" t="s">
         <v>5</v>
@@ -20561,13 +21064,13 @@
     </row>
     <row r="951" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B951" s="5">
-        <v>45886</v>
+        <v>45884</v>
       </c>
       <c r="C951" s="3" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="D951" s="7" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="E951" s="3" t="s">
         <v>5</v>
@@ -20575,13 +21078,13 @@
     </row>
     <row r="952" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B952" s="5">
-        <v>45889</v>
+        <v>45886</v>
       </c>
       <c r="C952" s="3" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="D952" s="7" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="E952" s="3" t="s">
         <v>5</v>
@@ -20592,7 +21095,7 @@
         <v>45889</v>
       </c>
       <c r="C953" s="3" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="D953" s="7" t="s">
         <v>1999</v>
@@ -20606,10 +21109,10 @@
         <v>45889</v>
       </c>
       <c r="C954" s="3" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D954" s="7" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="E954" s="3" t="s">
         <v>5</v>
@@ -20617,13 +21120,13 @@
     </row>
     <row r="955" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B955" s="5">
-        <v>45890</v>
+        <v>45889</v>
       </c>
       <c r="C955" s="3" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="D955" s="7" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="E955" s="3" t="s">
         <v>5</v>
@@ -20634,10 +21137,10 @@
         <v>45890</v>
       </c>
       <c r="C956" s="3" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="D956" s="7" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="E956" s="3" t="s">
         <v>5</v>
@@ -20648,10 +21151,10 @@
         <v>45890</v>
       </c>
       <c r="C957" s="3" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="D957" s="7" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="E957" s="3" t="s">
         <v>5</v>
@@ -20659,13 +21162,13 @@
     </row>
     <row r="958" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B958" s="5">
-        <v>45891</v>
+        <v>45890</v>
       </c>
       <c r="C958" s="3" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="D958" s="7" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="E958" s="3" t="s">
         <v>5</v>
@@ -20673,13 +21176,13 @@
     </row>
     <row r="959" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B959" s="5">
-        <v>45894</v>
+        <v>45891</v>
       </c>
       <c r="C959" s="3" t="s">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="D959" s="7" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E959" s="3" t="s">
         <v>5</v>
@@ -20690,7 +21193,7 @@
         <v>45894</v>
       </c>
       <c r="C960" s="3" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="D960" s="7" t="s">
         <v>2012</v>
@@ -20704,27 +21207,27 @@
         <v>45894</v>
       </c>
       <c r="C961" s="3" t="s">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="D961" s="7" t="s">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="E961" s="3" t="s">
-        <v>2023</v>
+        <v>5</v>
       </c>
     </row>
     <row r="962" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B962" s="5">
-        <v>45895</v>
+        <v>45894</v>
       </c>
       <c r="C962" s="3" t="s">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="D962" s="7" t="s">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="E962" s="3" t="s">
-        <v>5</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="963" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -20732,7 +21235,7 @@
         <v>45895</v>
       </c>
       <c r="C963" s="3" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="D963" s="7" t="s">
         <v>2015</v>
@@ -20743,13 +21246,13 @@
     </row>
     <row r="964" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B964" s="5">
-        <v>45896</v>
+        <v>45895</v>
       </c>
       <c r="C964" s="3" t="s">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="D964" s="7" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="E964" s="3" t="s">
         <v>5</v>
@@ -20757,13 +21260,13 @@
     </row>
     <row r="965" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B965" s="5">
-        <v>45897</v>
+        <v>45896</v>
       </c>
       <c r="C965" s="3" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="D965" s="7" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="E965" s="3" t="s">
         <v>5</v>
@@ -20771,13 +21274,13 @@
     </row>
     <row r="966" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B966" s="5">
-        <v>45898</v>
+        <v>45897</v>
       </c>
       <c r="C966" s="3" t="s">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="D966" s="7" t="s">
-        <v>2027</v>
+        <v>2020</v>
       </c>
       <c r="E966" s="3" t="s">
         <v>5</v>
@@ -20785,13 +21288,13 @@
     </row>
     <row r="967" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B967" s="5">
-        <v>45899</v>
+        <v>45898</v>
       </c>
       <c r="C967" s="3" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D967" s="7" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="E967" s="3" t="s">
         <v>5</v>
@@ -20799,27 +21302,27 @@
     </row>
     <row r="968" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B968" s="5">
+        <v>45899</v>
+      </c>
+      <c r="C968" s="3" t="s">
+        <v>2028</v>
+      </c>
+      <c r="D968" s="7" t="s">
+        <v>2029</v>
+      </c>
+      <c r="E968" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="969" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B969" s="5">
         <v>45900</v>
       </c>
-      <c r="C968" s="3" t="s">
+      <c r="C969" s="3" t="s">
         <v>2024</v>
       </c>
-      <c r="D968" s="7" t="s">
+      <c r="D969" s="7" t="s">
         <v>2025</v>
-      </c>
-      <c r="E968" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="969" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B969" s="10">
-        <v>45906</v>
-      </c>
-      <c r="C969" s="3" t="s">
-        <v>2044</v>
-      </c>
-      <c r="D969" s="7" t="s">
-        <v>2045</v>
       </c>
       <c r="E969" s="3" t="s">
         <v>5</v>
@@ -20827,27 +21330,27 @@
     </row>
     <row r="970" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B970" s="10">
+        <v>45906</v>
+      </c>
+      <c r="C970" s="3" t="s">
+        <v>2044</v>
+      </c>
+      <c r="D970" s="7" t="s">
+        <v>2045</v>
+      </c>
+      <c r="E970" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="971" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B971" s="10">
         <v>45907</v>
       </c>
-      <c r="C970" s="3" t="s">
+      <c r="C971" s="3" t="s">
         <v>2042</v>
       </c>
-      <c r="D970" s="7" t="s">
+      <c r="D971" s="7" t="s">
         <v>2043</v>
-      </c>
-      <c r="E970" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="971" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B971" s="5">
-        <v>45915</v>
-      </c>
-      <c r="C971" s="3" t="s">
-        <v>2030</v>
-      </c>
-      <c r="D971" s="7" t="s">
-        <v>2031</v>
       </c>
       <c r="E971" s="3" t="s">
         <v>5</v>
@@ -20855,13 +21358,13 @@
     </row>
     <row r="972" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B972" s="5">
-        <v>45918</v>
+        <v>45915</v>
       </c>
       <c r="C972" s="3" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="D972" s="7" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="E972" s="3" t="s">
         <v>5</v>
@@ -20869,13 +21372,13 @@
     </row>
     <row r="973" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B973" s="5">
-        <v>45919</v>
+        <v>45918</v>
       </c>
       <c r="C973" s="3" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="D973" s="7" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="E973" s="3" t="s">
         <v>5</v>
@@ -20883,13 +21386,13 @@
     </row>
     <row r="974" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B974" s="5">
-        <v>45922</v>
+        <v>45919</v>
       </c>
       <c r="C974" s="3" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="D974" s="7" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="E974" s="3" t="s">
         <v>5</v>
@@ -20897,13 +21400,13 @@
     </row>
     <row r="975" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B975" s="5">
-        <v>45930</v>
+        <v>45922</v>
       </c>
       <c r="C975" s="3" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="D975" s="7" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="E975" s="3" t="s">
         <v>5</v>
@@ -20911,27 +21414,27 @@
     </row>
     <row r="976" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B976" s="5">
-        <v>45932</v>
+        <v>45925</v>
       </c>
       <c r="C976" s="3" t="s">
-        <v>2040</v>
+        <v>2108</v>
       </c>
       <c r="D976" s="7" t="s">
-        <v>2041</v>
-      </c>
-      <c r="E976" s="3" t="s">
-        <v>5</v>
+        <v>2107</v>
+      </c>
+      <c r="E976" s="7" t="s">
+        <v>2109</v>
       </c>
     </row>
     <row r="977" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B977" s="5">
-        <v>45936</v>
+        <v>45930</v>
       </c>
       <c r="C977" s="3" t="s">
-        <v>2046</v>
+        <v>2038</v>
       </c>
       <c r="D977" s="7" t="s">
-        <v>2047</v>
+        <v>2039</v>
       </c>
       <c r="E977" s="3" t="s">
         <v>5</v>
@@ -20939,13 +21442,13 @@
     </row>
     <row r="978" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B978" s="5">
-        <v>45936</v>
+        <v>45932</v>
       </c>
       <c r="C978" s="3" t="s">
-        <v>2053</v>
+        <v>2040</v>
       </c>
       <c r="D978" s="7" t="s">
-        <v>2054</v>
+        <v>2041</v>
       </c>
       <c r="E978" s="3" t="s">
         <v>5</v>
@@ -20953,13 +21456,13 @@
     </row>
     <row r="979" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B979" s="5">
-        <v>45937</v>
+        <v>45936</v>
       </c>
       <c r="C979" s="3" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="D979" s="7" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="E979" s="3" t="s">
         <v>5</v>
@@ -20967,13 +21470,13 @@
     </row>
     <row r="980" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B980" s="5">
-        <v>45937</v>
+        <v>45936</v>
       </c>
       <c r="C980" s="3" t="s">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="D980" s="7" t="s">
-        <v>2049</v>
+        <v>2054</v>
       </c>
       <c r="E980" s="3" t="s">
         <v>5</v>
@@ -20984,10 +21487,10 @@
         <v>45937</v>
       </c>
       <c r="C981" s="3" t="s">
-        <v>2051</v>
+        <v>2048</v>
       </c>
       <c r="D981" s="7" t="s">
-        <v>2052</v>
+        <v>2049</v>
       </c>
       <c r="E981" s="3" t="s">
         <v>5</v>
@@ -20995,13 +21498,13 @@
     </row>
     <row r="982" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B982" s="5">
-        <v>45938</v>
+        <v>45937</v>
       </c>
       <c r="C982" s="3" t="s">
-        <v>2055</v>
+        <v>2050</v>
       </c>
       <c r="D982" s="7" t="s">
-        <v>2056</v>
+        <v>2049</v>
       </c>
       <c r="E982" s="3" t="s">
         <v>5</v>
@@ -21009,13 +21512,13 @@
     </row>
     <row r="983" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B983" s="5">
-        <v>45940</v>
+        <v>45937</v>
       </c>
       <c r="C983" s="3" t="s">
-        <v>2057</v>
+        <v>2051</v>
       </c>
       <c r="D983" s="7" t="s">
-        <v>2058</v>
+        <v>2052</v>
       </c>
       <c r="E983" s="3" t="s">
         <v>5</v>
@@ -21023,13 +21526,13 @@
     </row>
     <row r="984" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B984" s="5">
-        <v>45940</v>
+        <v>45938</v>
       </c>
       <c r="C984" s="3" t="s">
-        <v>2059</v>
+        <v>2055</v>
       </c>
       <c r="D984" s="7" t="s">
-        <v>2060</v>
+        <v>2056</v>
       </c>
       <c r="E984" s="3" t="s">
         <v>5</v>
@@ -21037,13 +21540,13 @@
     </row>
     <row r="985" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B985" s="5">
-        <v>45942</v>
+        <v>45940</v>
       </c>
       <c r="C985" s="3" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="D985" s="7" t="s">
-        <v>2062</v>
+        <v>2058</v>
       </c>
       <c r="E985" s="3" t="s">
         <v>5</v>
@@ -21051,13 +21554,13 @@
     </row>
     <row r="986" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B986" s="5">
-        <v>45943</v>
+        <v>45940</v>
       </c>
       <c r="C986" s="3" t="s">
-        <v>2063</v>
+        <v>2059</v>
       </c>
       <c r="D986" s="7" t="s">
-        <v>2064</v>
+        <v>2060</v>
       </c>
       <c r="E986" s="3" t="s">
         <v>5</v>
@@ -21065,13 +21568,13 @@
     </row>
     <row r="987" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B987" s="5">
-        <v>45943</v>
+        <v>45942</v>
       </c>
       <c r="C987" s="3" t="s">
-        <v>2065</v>
+        <v>2061</v>
       </c>
       <c r="D987" s="7" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="E987" s="3" t="s">
         <v>5</v>
@@ -21079,13 +21582,13 @@
     </row>
     <row r="988" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B988" s="5">
-        <v>45944</v>
+        <v>45943</v>
       </c>
       <c r="C988" s="3" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
       <c r="D988" s="7" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
       <c r="E988" s="3" t="s">
         <v>5</v>
@@ -21093,13 +21596,13 @@
     </row>
     <row r="989" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B989" s="5">
-        <v>45944</v>
+        <v>45943</v>
       </c>
       <c r="C989" s="3" t="s">
-        <v>2068</v>
+        <v>2065</v>
       </c>
       <c r="D989" s="7" t="s">
-        <v>2069</v>
+        <v>2064</v>
       </c>
       <c r="E989" s="3" t="s">
         <v>5</v>
@@ -21110,10 +21613,10 @@
         <v>45944</v>
       </c>
       <c r="C990" s="3" t="s">
-        <v>2074</v>
+        <v>2066</v>
       </c>
       <c r="D990" s="7" t="s">
-        <v>2075</v>
+        <v>2067</v>
       </c>
       <c r="E990" s="3" t="s">
         <v>5</v>
@@ -21121,13 +21624,13 @@
     </row>
     <row r="991" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B991" s="5">
-        <v>45945</v>
+        <v>45944</v>
       </c>
       <c r="C991" s="3" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
       <c r="D991" s="7" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="E991" s="3" t="s">
         <v>5</v>
@@ -21135,13 +21638,13 @@
     </row>
     <row r="992" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B992" s="5">
-        <v>45945</v>
+        <v>45944</v>
       </c>
       <c r="C992" s="3" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
       <c r="D992" s="7" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="E992" s="3" t="s">
         <v>5</v>
@@ -21149,13 +21652,13 @@
     </row>
     <row r="993" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B993" s="5">
-        <v>45946</v>
+        <v>45945</v>
       </c>
       <c r="C993" s="3" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
       <c r="D993" s="7" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="E993" s="3" t="s">
         <v>5</v>
@@ -21163,13 +21666,13 @@
     </row>
     <row r="994" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B994" s="5">
-        <v>45946</v>
+        <v>45945</v>
       </c>
       <c r="C994" s="3" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="D994" s="7" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="E994" s="3" t="s">
         <v>5</v>
@@ -21180,80 +21683,80 @@
         <v>45946</v>
       </c>
       <c r="C995" s="3" t="s">
+        <v>2072</v>
+      </c>
+      <c r="D995" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="E995" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="996" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B996" s="5">
+        <v>45946</v>
+      </c>
+      <c r="C996" s="3" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D996" s="7" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E996" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="997" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B997" s="5">
+        <v>45946</v>
+      </c>
+      <c r="C997" s="3" t="s">
         <v>2080</v>
       </c>
-      <c r="D995" s="7" t="s">
+      <c r="D997" s="7" t="s">
         <v>2081</v>
       </c>
-      <c r="E995" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="996" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B996" s="5">
+      <c r="E997" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="998" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B998" s="5">
         <v>45947</v>
       </c>
-      <c r="C996" s="3" t="s">
+      <c r="C998" s="3" t="s">
         <v>2082</v>
       </c>
-      <c r="D996" s="7" t="s">
+      <c r="D998" s="7" t="s">
         <v>2083</v>
       </c>
-      <c r="E996" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="997" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B997" s="5">
+      <c r="E998" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="999" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B999" s="5">
         <v>45947</v>
       </c>
-      <c r="C997" s="3" t="s">
+      <c r="C999" s="3" t="s">
         <v>2086</v>
       </c>
-      <c r="D997" s="7" t="s">
+      <c r="D999" s="7" t="s">
         <v>2087</v>
       </c>
-      <c r="E997" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="998" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B998" s="10">
+      <c r="E999" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1000" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B1000" s="10">
         <v>45948</v>
       </c>
-      <c r="C998" t="s">
+      <c r="C1000" t="s">
         <v>2084</v>
       </c>
-      <c r="D998" s="7" t="s">
+      <c r="D1000" s="7" t="s">
         <v>2085</v>
-      </c>
-      <c r="E998" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="999" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B999" s="10">
-        <v>45951</v>
-      </c>
-      <c r="C999" s="7" t="s">
-        <v>2088</v>
-      </c>
-      <c r="D999" s="7" t="s">
-        <v>2089</v>
-      </c>
-      <c r="E999" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="1000" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1000" s="10">
-        <v>45952</v>
-      </c>
-      <c r="C1000" s="3" t="s">
-        <v>2090</v>
-      </c>
-      <c r="D1000" s="7" t="s">
-        <v>2091</v>
       </c>
       <c r="E1000" s="3" t="s">
         <v>5</v>
@@ -21261,13 +21764,13 @@
     </row>
     <row r="1001" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1001" s="10">
-        <v>45952</v>
+        <v>45950</v>
       </c>
       <c r="C1001" s="3" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="D1001" s="7" t="s">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="E1001" s="3" t="s">
         <v>5</v>
@@ -21275,13 +21778,13 @@
     </row>
     <row r="1002" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1002" s="10">
-        <v>45953</v>
-      </c>
-      <c r="C1002" s="3" t="s">
-        <v>2092</v>
+        <v>45951</v>
+      </c>
+      <c r="C1002" s="7" t="s">
+        <v>2088</v>
       </c>
       <c r="D1002" s="7" t="s">
-        <v>2093</v>
+        <v>2089</v>
       </c>
       <c r="E1002" s="3" t="s">
         <v>5</v>
@@ -21289,103 +21792,1169 @@
     </row>
     <row r="1003" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1003" s="10">
+        <v>45952</v>
+      </c>
+      <c r="C1003" s="3" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D1003" s="7" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1003" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1004" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1004" s="10">
+        <v>45952</v>
+      </c>
+      <c r="C1004" s="3" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1004" s="7" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E1004" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1005" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1005" s="10">
         <v>45953</v>
       </c>
-      <c r="C1003" s="3" t="s">
+      <c r="C1005" s="3" t="s">
+        <v>2092</v>
+      </c>
+      <c r="D1005" s="7" t="s">
+        <v>2093</v>
+      </c>
+      <c r="E1005" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1006" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1006" s="10">
+        <v>45953</v>
+      </c>
+      <c r="C1006" s="3" t="s">
         <v>2094</v>
       </c>
-      <c r="D1003" s="7" t="s">
+      <c r="D1006" s="7" t="s">
         <v>2095</v>
       </c>
-      <c r="E1003" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="1004" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1005" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1006" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1007" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1008" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1009" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1010" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1011" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1012" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1013" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1014" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1015" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1016" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1017" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1018" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1019" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1020" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1021" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1022" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1023" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1024" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1025" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1026" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1027" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1028" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1029" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1030" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1031" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1032" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1033" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1034" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1035" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1036" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1037" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1038" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1039" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1040" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1041" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1042" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1043" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1044" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1045" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1046" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1047" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1048" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1049" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1050" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1051" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1052" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1053" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1054" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1055" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1056" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1057" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1058" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1059" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1060" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1061" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1062" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1063" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1064" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1065" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1066" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1067" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1068" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1069" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1070" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1071" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1072" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1073" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1074" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1075" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1076" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1077" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1078" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1079" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1080" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1081" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1082" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1083" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1084" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1085" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1086" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1087" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1088" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="E1006" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1007" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1007" s="10">
+        <v>45953</v>
+      </c>
+      <c r="C1007" s="3" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D1007" s="7" t="s">
+        <v>2103</v>
+      </c>
+      <c r="E1007" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1008" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1008" s="10">
+        <v>45954</v>
+      </c>
+      <c r="C1008" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="D1008" s="7" t="s">
+        <v>2101</v>
+      </c>
+      <c r="E1008" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1009" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1009" s="10">
+        <v>45954</v>
+      </c>
+      <c r="C1009" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="D1009" s="7" t="s">
+        <v>2104</v>
+      </c>
+      <c r="E1009" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1010" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1010" s="10">
+        <v>45956</v>
+      </c>
+      <c r="C1010" s="3" t="s">
+        <v>2110</v>
+      </c>
+      <c r="D1010" s="7" t="s">
+        <v>2111</v>
+      </c>
+      <c r="E1010" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1011" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1011" s="10">
+        <v>45956</v>
+      </c>
+      <c r="C1011" s="3" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D1011" s="7" t="s">
+        <v>2119</v>
+      </c>
+      <c r="E1011" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1012" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1012" s="10">
+        <v>45957</v>
+      </c>
+      <c r="C1012" s="3" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D1012" s="7" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E1012" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1013" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1013" s="10">
+        <v>45959</v>
+      </c>
+      <c r="C1013" s="3" t="s">
+        <v>2112</v>
+      </c>
+      <c r="D1013" s="7" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1013" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1014" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1014" s="10">
+        <v>45959</v>
+      </c>
+      <c r="C1014" s="3" t="s">
+        <v>2114</v>
+      </c>
+      <c r="D1014" s="7" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1014" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1015" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1015" s="10">
+        <v>45960</v>
+      </c>
+      <c r="C1015" s="3" t="s">
+        <v>2120</v>
+      </c>
+      <c r="D1015" s="7" t="s">
+        <v>2121</v>
+      </c>
+      <c r="E1015" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1016" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1016" s="10">
+        <v>45960</v>
+      </c>
+      <c r="C1016" s="3" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D1016" s="7" t="s">
+        <v>2123</v>
+      </c>
+      <c r="E1016" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1017" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1017" s="10">
+        <v>45961</v>
+      </c>
+      <c r="C1017" s="3" t="s">
+        <v>2132</v>
+      </c>
+      <c r="D1017" s="7" t="s">
+        <v>2133</v>
+      </c>
+      <c r="E1017" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1018" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1018" s="10">
+        <v>45962</v>
+      </c>
+      <c r="C1018" s="3" t="s">
+        <v>2124</v>
+      </c>
+      <c r="D1018" s="7" t="s">
+        <v>2125</v>
+      </c>
+      <c r="E1018" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1019" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1019" s="10">
+        <v>45964</v>
+      </c>
+      <c r="C1019" s="3" t="s">
+        <v>2126</v>
+      </c>
+      <c r="D1019" s="7" t="s">
+        <v>2127</v>
+      </c>
+      <c r="E1019" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1020" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1020" s="10">
+        <v>45965</v>
+      </c>
+      <c r="C1020" s="3" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D1020" s="7" t="s">
+        <v>2129</v>
+      </c>
+      <c r="E1020" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1021" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1021" s="10">
+        <v>45965</v>
+      </c>
+      <c r="C1021" s="3" t="s">
+        <v>2130</v>
+      </c>
+      <c r="D1021" s="7" t="s">
+        <v>2131</v>
+      </c>
+      <c r="E1021" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1022" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1022" s="10">
+        <v>45967</v>
+      </c>
+      <c r="C1022" s="3" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D1022" s="7" t="s">
+        <v>2135</v>
+      </c>
+      <c r="E1022" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1023" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1023" s="10">
+        <v>45969</v>
+      </c>
+      <c r="C1023" s="3" t="s">
+        <v>2136</v>
+      </c>
+      <c r="D1023" s="7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="E1023" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1024" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1024" s="10">
+        <v>45970</v>
+      </c>
+      <c r="C1024" s="3" t="s">
+        <v>2138</v>
+      </c>
+      <c r="D1024" s="7" t="s">
+        <v>2139</v>
+      </c>
+      <c r="E1024" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1025" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1025" s="10">
+        <v>45971</v>
+      </c>
+      <c r="C1025" s="3" t="s">
+        <v>2140</v>
+      </c>
+      <c r="D1025" s="7" t="s">
+        <v>2141</v>
+      </c>
+      <c r="E1025" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1026" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1026" s="10">
+        <v>45971</v>
+      </c>
+      <c r="C1026" s="3" t="s">
+        <v>2142</v>
+      </c>
+      <c r="D1026" s="7" t="s">
+        <v>2143</v>
+      </c>
+      <c r="E1026" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1027" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1027" s="10">
+        <v>45972</v>
+      </c>
+      <c r="C1027" s="3" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D1027" s="7" t="s">
+        <v>2141</v>
+      </c>
+      <c r="E1027" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1028" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1028" s="10">
+        <v>45973</v>
+      </c>
+      <c r="C1028" s="3" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D1028" s="7" t="s">
+        <v>2145</v>
+      </c>
+      <c r="E1028" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1029" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1029" s="10">
+        <v>45973</v>
+      </c>
+      <c r="C1029" s="3" t="s">
+        <v>2147</v>
+      </c>
+      <c r="D1029" s="7" t="s">
+        <v>2148</v>
+      </c>
+      <c r="E1029" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1030" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1030" s="10">
+        <v>45973</v>
+      </c>
+      <c r="C1030" s="3" t="s">
+        <v>2149</v>
+      </c>
+      <c r="D1030" s="7" t="s">
+        <v>2150</v>
+      </c>
+      <c r="E1030" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1031" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1031" s="10">
+        <v>45974</v>
+      </c>
+      <c r="C1031" s="3" t="s">
+        <v>2155</v>
+      </c>
+      <c r="D1031" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="E1031" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1032" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1032" s="10">
+        <v>45975</v>
+      </c>
+      <c r="C1032" s="3" t="s">
+        <v>2151</v>
+      </c>
+      <c r="D1032" s="7" t="s">
+        <v>2152</v>
+      </c>
+      <c r="E1032" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1033" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1033" s="10">
+        <v>45975</v>
+      </c>
+      <c r="C1033" s="3" t="s">
+        <v>2153</v>
+      </c>
+      <c r="D1033" s="7" t="s">
+        <v>2154</v>
+      </c>
+      <c r="E1033" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1034" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1034" s="10">
+        <v>45975</v>
+      </c>
+      <c r="C1034" s="3" t="s">
+        <v>2157</v>
+      </c>
+      <c r="D1034" s="7" t="s">
+        <v>2158</v>
+      </c>
+      <c r="E1034" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1035" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1035" s="10">
+        <v>45975</v>
+      </c>
+      <c r="C1035" s="3" t="s">
+        <v>2163</v>
+      </c>
+      <c r="D1035" s="7" t="s">
+        <v>2164</v>
+      </c>
+      <c r="E1035" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1036" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1036" s="10">
+        <v>45975</v>
+      </c>
+      <c r="C1036" s="3" t="s">
+        <v>2166</v>
+      </c>
+      <c r="D1036" s="7" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1036" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1037" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1037" s="10">
+        <v>45976</v>
+      </c>
+      <c r="C1037" s="3" t="s">
+        <v>2159</v>
+      </c>
+      <c r="D1037" s="7" t="s">
+        <v>2160</v>
+      </c>
+      <c r="E1037" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1038" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1038" s="10">
+        <v>45976</v>
+      </c>
+      <c r="C1038" s="3" t="s">
+        <v>2161</v>
+      </c>
+      <c r="D1038" s="7" t="s">
+        <v>2162</v>
+      </c>
+      <c r="E1038" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1039" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1039" s="10">
+        <v>45977</v>
+      </c>
+      <c r="C1039" s="3" t="s">
+        <v>2169</v>
+      </c>
+      <c r="D1039" s="7" t="s">
+        <v>2170</v>
+      </c>
+      <c r="E1039" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1040" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1040" s="10">
+        <v>45978</v>
+      </c>
+      <c r="C1040" s="3" t="s">
+        <v>2167</v>
+      </c>
+      <c r="D1040" s="7" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E1040" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1041" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1041" s="10">
+        <v>45978</v>
+      </c>
+      <c r="C1041" s="3" t="s">
+        <v>2171</v>
+      </c>
+      <c r="D1041" s="7" t="s">
+        <v>2172</v>
+      </c>
+      <c r="E1041" s="3" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="1042" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1042" s="10">
+        <v>45979</v>
+      </c>
+      <c r="C1042" s="3" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D1042" s="7" t="s">
+        <v>2175</v>
+      </c>
+      <c r="E1042" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1043" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1043" s="10">
+        <v>45979</v>
+      </c>
+      <c r="C1043" s="3" t="s">
+        <v>2176</v>
+      </c>
+      <c r="D1043" s="7" t="s">
+        <v>2177</v>
+      </c>
+      <c r="E1043" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1044" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1044" s="10">
+        <v>45980</v>
+      </c>
+      <c r="C1044" s="3" t="s">
+        <v>2178</v>
+      </c>
+      <c r="D1044" s="7" t="s">
+        <v>2179</v>
+      </c>
+      <c r="E1044" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1045" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1045" s="10">
+        <v>45980</v>
+      </c>
+      <c r="C1045" s="3" t="s">
+        <v>2182</v>
+      </c>
+      <c r="D1045" s="7" t="s">
+        <v>2183</v>
+      </c>
+      <c r="E1045" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1046" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1046" s="10">
+        <v>45981</v>
+      </c>
+      <c r="C1046" s="3" t="s">
+        <v>2180</v>
+      </c>
+      <c r="D1046" s="7" t="s">
+        <v>2181</v>
+      </c>
+      <c r="E1046" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1047" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1047" s="10">
+        <v>45982</v>
+      </c>
+      <c r="C1047" s="3" t="s">
+        <v>2184</v>
+      </c>
+      <c r="D1047" s="7" t="s">
+        <v>2185</v>
+      </c>
+      <c r="E1047" s="2" t="s">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="1048" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1048" s="10">
+        <v>45983</v>
+      </c>
+      <c r="C1048" s="3" t="s">
+        <v>2188</v>
+      </c>
+      <c r="D1048" s="7" t="s">
+        <v>2189</v>
+      </c>
+      <c r="E1048" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1049" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1049" s="10">
+        <v>45984</v>
+      </c>
+      <c r="C1049" s="3" t="s">
+        <v>2186</v>
+      </c>
+      <c r="D1049" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="E1049" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1050" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1050" s="10">
+        <v>45986</v>
+      </c>
+      <c r="C1050" s="3" t="s">
+        <v>2190</v>
+      </c>
+      <c r="D1050" s="7" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1050" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1051" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1051" s="10">
+        <v>45986</v>
+      </c>
+      <c r="C1051" s="3" t="s">
+        <v>2192</v>
+      </c>
+      <c r="D1051" s="7" t="s">
+        <v>2193</v>
+      </c>
+      <c r="E1051" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1052" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1052" s="10">
+        <v>45987</v>
+      </c>
+      <c r="C1052" s="3" t="s">
+        <v>2194</v>
+      </c>
+      <c r="D1052" s="7" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1052" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1053" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1053" s="10">
+        <v>45987</v>
+      </c>
+      <c r="C1053" s="3" t="s">
+        <v>2196</v>
+      </c>
+      <c r="D1053" s="7" t="s">
+        <v>2197</v>
+      </c>
+      <c r="E1053" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1054" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1054" s="10">
+        <v>45987</v>
+      </c>
+      <c r="C1054" s="3" t="s">
+        <v>2198</v>
+      </c>
+      <c r="D1054" s="7" t="s">
+        <v>2199</v>
+      </c>
+      <c r="E1054" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1055" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1055" s="10">
+        <v>45989</v>
+      </c>
+      <c r="C1055" s="3" t="s">
+        <v>2200</v>
+      </c>
+      <c r="D1055" s="7" t="s">
+        <v>2201</v>
+      </c>
+      <c r="E1055" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1056" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1056" s="10">
+        <v>45989</v>
+      </c>
+      <c r="C1056" s="3" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D1056" s="7" t="s">
+        <v>2203</v>
+      </c>
+      <c r="E1056" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1057" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1057" s="10">
+        <v>45989</v>
+      </c>
+      <c r="C1057" s="3" t="s">
+        <v>2204</v>
+      </c>
+      <c r="D1057" s="7" t="s">
+        <v>2205</v>
+      </c>
+      <c r="E1057" s="3" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="1058" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1058" s="10">
+        <v>45989</v>
+      </c>
+      <c r="C1058" s="3" t="s">
+        <v>2207</v>
+      </c>
+      <c r="D1058" s="7" t="s">
+        <v>2208</v>
+      </c>
+      <c r="E1058" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1059" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1059" s="10">
+        <v>45990</v>
+      </c>
+      <c r="C1059" s="3" t="s">
+        <v>2209</v>
+      </c>
+      <c r="D1059" s="7" t="s">
+        <v>2210</v>
+      </c>
+      <c r="E1059" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1060" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1060" s="10">
+        <v>45990</v>
+      </c>
+      <c r="C1060" s="3" t="s">
+        <v>2211</v>
+      </c>
+      <c r="D1060" s="7" t="s">
+        <v>2212</v>
+      </c>
+      <c r="E1060" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1061" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1061" s="10">
+        <v>45990</v>
+      </c>
+      <c r="C1061" s="3" t="s">
+        <v>2213</v>
+      </c>
+      <c r="D1061" s="7" t="s">
+        <v>2214</v>
+      </c>
+      <c r="E1061" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1062" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1062" s="10">
+        <v>45990</v>
+      </c>
+      <c r="C1062" s="3" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D1062" s="7" t="s">
+        <v>2212</v>
+      </c>
+      <c r="E1062" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1063" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1063" s="10">
+        <v>45990</v>
+      </c>
+      <c r="C1063" s="3" t="s">
+        <v>2216</v>
+      </c>
+      <c r="D1063" s="7" t="s">
+        <v>2217</v>
+      </c>
+      <c r="E1063" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1064" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1064" s="10">
+        <v>45991</v>
+      </c>
+      <c r="C1064" s="3" t="s">
+        <v>2218</v>
+      </c>
+      <c r="D1064" s="7" t="s">
+        <v>2219</v>
+      </c>
+      <c r="E1064" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1065" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1065" s="10">
+        <v>45991</v>
+      </c>
+      <c r="C1065" s="3" t="s">
+        <v>2220</v>
+      </c>
+      <c r="D1065" s="7" t="s">
+        <v>2221</v>
+      </c>
+      <c r="E1065" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1066" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1066" s="10">
+        <v>45991</v>
+      </c>
+      <c r="C1066" s="3" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D1066" s="7" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E1066" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1067" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1067" s="10">
+        <v>45992</v>
+      </c>
+      <c r="C1067" s="3" t="s">
+        <v>2227</v>
+      </c>
+      <c r="D1067" s="7" t="s">
+        <v>2226</v>
+      </c>
+      <c r="E1067" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1068" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1068" s="10">
+        <v>45992</v>
+      </c>
+      <c r="C1068" s="3" t="s">
+        <v>2225</v>
+      </c>
+      <c r="D1068" s="7" t="s">
+        <v>2226</v>
+      </c>
+      <c r="E1068" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1069" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1069" s="10">
+        <v>45992</v>
+      </c>
+      <c r="C1069" s="3" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1069" s="2" t="s">
+        <v>2229</v>
+      </c>
+      <c r="E1069" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1070" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1070" s="10">
+        <v>45993</v>
+      </c>
+      <c r="C1070" s="3" t="s">
+        <v>2230</v>
+      </c>
+      <c r="D1070" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="E1070" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1071" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1071" s="10">
+        <v>45995</v>
+      </c>
+      <c r="C1071" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D1071" s="7" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E1071" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1072" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1072" s="10">
+        <v>45995</v>
+      </c>
+      <c r="C1072" s="3" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D1072" s="7" t="s">
+        <v>2237</v>
+      </c>
+      <c r="E1072" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1073" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1073" s="10">
+        <v>45996</v>
+      </c>
+      <c r="C1073" s="3" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D1073" s="7" t="s">
+        <v>2233</v>
+      </c>
+      <c r="E1073" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1074" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1074" s="10">
+        <v>46000</v>
+      </c>
+      <c r="C1074" s="3" t="s">
+        <v>2240</v>
+      </c>
+      <c r="D1074" s="7" t="s">
+        <v>2241</v>
+      </c>
+      <c r="E1074" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1075" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1075" s="10">
+        <v>46001</v>
+      </c>
+      <c r="C1075" s="3" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D1075" s="2" t="s">
+        <v>2239</v>
+      </c>
+      <c r="E1075" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1076" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1076" s="10">
+        <v>46001</v>
+      </c>
+      <c r="C1076" s="3" t="s">
+        <v>2242</v>
+      </c>
+      <c r="D1076" s="7" t="s">
+        <v>2243</v>
+      </c>
+      <c r="E1076" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1077" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1077" s="10">
+        <v>46001</v>
+      </c>
+      <c r="C1077" s="3" t="s">
+        <v>2244</v>
+      </c>
+      <c r="D1077" s="7" t="s">
+        <v>2245</v>
+      </c>
+      <c r="E1077" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1078" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1078" s="10">
+        <v>46003</v>
+      </c>
+      <c r="C1078" s="3" t="s">
+        <v>2248</v>
+      </c>
+      <c r="D1078" s="7" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E1078" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1079" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1079" s="10">
+        <v>46007</v>
+      </c>
+      <c r="C1079" s="3" t="s">
+        <v>2246</v>
+      </c>
+      <c r="D1079" s="7" t="s">
+        <v>2247</v>
+      </c>
+      <c r="E1079" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1080" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1080" s="10">
+        <v>46009</v>
+      </c>
+      <c r="C1080" s="3" t="s">
+        <v>2250</v>
+      </c>
+      <c r="D1080" s="7" t="s">
+        <v>2251</v>
+      </c>
+      <c r="E1080" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1081" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1081" s="10">
+        <v>46010</v>
+      </c>
+      <c r="C1081" s="3" t="s">
+        <v>2256</v>
+      </c>
+      <c r="D1081" s="7" t="s">
+        <v>2257</v>
+      </c>
+      <c r="E1081" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1082" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1082" s="10">
+        <v>46013</v>
+      </c>
+      <c r="C1082" s="3" t="s">
+        <v>2252</v>
+      </c>
+      <c r="D1082" s="7" t="s">
+        <v>2253</v>
+      </c>
+      <c r="E1082" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1083" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1083" s="10">
+        <v>46013</v>
+      </c>
+      <c r="C1083" s="3" t="s">
+        <v>2254</v>
+      </c>
+      <c r="D1083" s="7" t="s">
+        <v>2255</v>
+      </c>
+      <c r="E1083" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1084" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1084" s="10">
+        <v>46017</v>
+      </c>
+      <c r="C1084" s="3" t="s">
+        <v>2258</v>
+      </c>
+      <c r="D1084" s="7" t="s">
+        <v>2259</v>
+      </c>
+      <c r="E1084" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1085" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1085" s="10">
+        <v>46020</v>
+      </c>
+      <c r="C1085" s="3" t="s">
+        <v>2260</v>
+      </c>
+      <c r="D1085" s="7" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E1085" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1086" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1087" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1088" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1089" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1090" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1091" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -21418,9 +22987,29 @@
     <row r="1118" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1119" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1120" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1121" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1122" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1123" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2C9FCD8-4C9B-461A-9B2C-6E5CBB687676}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="5" width="101.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>